--- a/braph2individualconnectome/pipelines/neuroimaging conversion structural/Example data NIfTI/reference_data/pdf_wmprob/sub-0007_ses-01_WMprob_pdf.xlsx
+++ b/braph2individualconnectome/pipelines/neuroimaging conversion structural/Example data NIfTI/reference_data/pdf_wmprob/sub-0007_ses-01_WMprob_pdf.xlsx
@@ -1,6 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <fileVersion appName="libxl" rupBuild="4.6.0"/>
   <workbookPr/>
   <bookViews>
     <workbookView activeTab="0"/>
@@ -885,7 +886,7 @@
         <v>0</v>
       </c>
       <c r="F22" s="0">
-        <v>0.0018193064803696812</v>
+        <v>0</v>
       </c>
       <c r="G22" s="0">
         <v>0</v>
@@ -894,7 +895,7 @@
         <v>0</v>
       </c>
       <c r="I22" s="0">
-        <v>0.0019860578737264387</v>
+        <v>0</v>
       </c>
       <c r="J22" s="0">
         <v>0</v>
@@ -908,7 +909,7 @@
     </row>
     <row r="23">
       <c r="A23" s="0">
-        <v>0.0024613566998129346</v>
+        <v>0</v>
       </c>
       <c r="B23" s="0">
         <v>0</v>
@@ -920,7 +921,7 @@
         <v>0</v>
       </c>
       <c r="E23" s="0">
-        <v>0.0005966765118291113</v>
+        <v>0</v>
       </c>
       <c r="F23" s="0">
         <v>0</v>
@@ -932,7 +933,7 @@
         <v>0</v>
       </c>
       <c r="I23" s="0">
-        <v>0.0019860578737264387</v>
+        <v>0</v>
       </c>
       <c r="J23" s="0">
         <v>0</v>
@@ -946,31 +947,31 @@
     </row>
     <row r="24">
       <c r="A24" s="0">
-        <v>0.0098454267992517663</v>
+        <v>0</v>
       </c>
       <c r="B24" s="0">
-        <v>0.17543859649122839</v>
+        <v>0</v>
       </c>
       <c r="C24" s="0">
-        <v>0.0012680860776829556</v>
+        <v>0</v>
       </c>
       <c r="D24" s="0">
         <v>0</v>
       </c>
       <c r="E24" s="0">
-        <v>0.003580059070974678</v>
+        <v>0</v>
       </c>
       <c r="F24" s="0">
-        <v>0.0018193064803696864</v>
+        <v>0</v>
       </c>
       <c r="G24" s="0">
         <v>0</v>
       </c>
       <c r="H24" s="0">
-        <v>0.011361699710276679</v>
+        <v>0</v>
       </c>
       <c r="I24" s="0">
-        <v>0.0099302893686322204</v>
+        <v>0</v>
       </c>
       <c r="J24" s="0">
         <v>0</v>
@@ -984,37 +985,37 @@
     </row>
     <row r="25">
       <c r="A25" s="0">
-        <v>0.0024613566998129346</v>
+        <v>0</v>
       </c>
       <c r="B25" s="0">
         <v>0</v>
       </c>
       <c r="C25" s="0">
-        <v>0.0038042582330488559</v>
+        <v>0</v>
       </c>
       <c r="D25" s="0">
-        <v>0.0096170028610583439</v>
+        <v>0</v>
       </c>
       <c r="E25" s="0">
-        <v>0.0059667651182911136</v>
+        <v>0.0011933530236582226</v>
       </c>
       <c r="F25" s="0">
-        <v>0.0090965324018484079</v>
+        <v>0</v>
       </c>
       <c r="G25" s="0">
-        <v>0.080466706900020044</v>
+        <v>0</v>
       </c>
       <c r="H25" s="0">
-        <v>0.039765948985968268</v>
+        <v>0</v>
       </c>
       <c r="I25" s="0">
-        <v>0.02780481023217014</v>
+        <v>0.0019860578737264387</v>
       </c>
       <c r="J25" s="0">
-        <v>0.03680529996319467</v>
+        <v>0</v>
       </c>
       <c r="K25" s="0">
-        <v>0.12886597938144317</v>
+        <v>0</v>
       </c>
       <c r="L25" s="0">
         <v>0.0015550648462040854</v>
@@ -1022,37 +1023,37 @@
     </row>
     <row r="26">
       <c r="A26" s="0">
-        <v>0.03692035049719402</v>
+        <v>0</v>
       </c>
       <c r="B26" s="0">
-        <v>0.35087719298245584</v>
+        <v>0</v>
       </c>
       <c r="C26" s="0">
-        <v>0.024093635475976087</v>
+        <v>0.001268086077682952</v>
       </c>
       <c r="D26" s="0">
-        <v>0.016829755006852101</v>
+        <v>0</v>
       </c>
       <c r="E26" s="0">
-        <v>0.028043796055968229</v>
+        <v>0.0011933530236582226</v>
       </c>
       <c r="F26" s="0">
-        <v>0.02365098424480586</v>
+        <v>0</v>
       </c>
       <c r="G26" s="0">
-        <v>0.20116676725005009</v>
+        <v>0</v>
       </c>
       <c r="H26" s="0">
-        <v>0.15338294608873473</v>
+        <v>0</v>
       </c>
       <c r="I26" s="0">
-        <v>0.057595678338066718</v>
+        <v>0.0039721157474528774</v>
       </c>
       <c r="J26" s="0">
-        <v>0.11041589988958402</v>
+        <v>0</v>
       </c>
       <c r="K26" s="0">
-        <v>0.12886597938144317</v>
+        <v>0</v>
       </c>
       <c r="L26" s="0">
         <v>0.0015550648462040854</v>
@@ -1060,2773 +1061,2773 @@
     </row>
     <row r="27">
       <c r="A27" s="0">
-        <v>0.071379344294575112</v>
+        <v>0</v>
       </c>
       <c r="B27" s="0">
-        <v>0.70175438596491169</v>
+        <v>0</v>
       </c>
       <c r="C27" s="0">
-        <v>0.053259615262683982</v>
+        <v>0.001268086077682952</v>
       </c>
       <c r="D27" s="0">
-        <v>0.076936022888466751</v>
+        <v>0</v>
       </c>
       <c r="E27" s="0">
-        <v>0.052507533040961799</v>
+        <v>0.0065634416301202248</v>
       </c>
       <c r="F27" s="0">
-        <v>0.054579194411090444</v>
+        <v>0.0018193064803696812</v>
       </c>
       <c r="G27" s="0">
-        <v>0.18105009052504509</v>
+        <v>0</v>
       </c>
       <c r="H27" s="0">
-        <v>0.3124467420326078</v>
+        <v>0</v>
       </c>
       <c r="I27" s="0">
-        <v>0.18668944013028524</v>
+        <v>0.0059581736211793161</v>
       </c>
       <c r="J27" s="0">
-        <v>0.42326094957673871</v>
+        <v>0</v>
       </c>
       <c r="K27" s="0">
         <v>0.12886597938144317</v>
       </c>
       <c r="L27" s="0">
-        <v>0.0031101296924081708</v>
+        <v>0.0093303890772245112</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="0">
-        <v>0.19444717928522184</v>
+        <v>0</v>
       </c>
       <c r="B28" s="0">
-        <v>1.4912280701754372</v>
+        <v>0.17543859649122792</v>
       </c>
       <c r="C28" s="0">
-        <v>0.14075755462280767</v>
+        <v>0.020289377242927231</v>
       </c>
       <c r="D28" s="0">
-        <v>0.19234005722116684</v>
+        <v>0.004808501430529172</v>
       </c>
       <c r="E28" s="0">
-        <v>0.14320236283898671</v>
+        <v>0.022077030937677121</v>
       </c>
       <c r="F28" s="0">
-        <v>0.12007422770439899</v>
+        <v>0.0018193064803696812</v>
       </c>
       <c r="G28" s="0">
-        <v>0.46268356467511529</v>
+        <v>0</v>
       </c>
       <c r="H28" s="0">
-        <v>0.63057433392035389</v>
+        <v>0</v>
       </c>
       <c r="I28" s="0">
-        <v>0.3694067645131176</v>
+        <v>0.031776925979623019</v>
       </c>
       <c r="J28" s="0">
-        <v>0.90172984909826925</v>
+        <v>0</v>
       </c>
       <c r="K28" s="0">
-        <v>0.77319587628865916</v>
+        <v>0</v>
       </c>
       <c r="L28" s="0">
-        <v>0.013995583615836769</v>
+        <v>0.023325972693061282</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="0">
-        <v>0.40858521216894944</v>
+        <v>0.0098454267992517941</v>
       </c>
       <c r="B29" s="0">
-        <v>2.1052631578947465</v>
+        <v>0</v>
       </c>
       <c r="C29" s="0">
-        <v>0.31575343334305678</v>
+        <v>0.044383012718903568</v>
       </c>
       <c r="D29" s="0">
-        <v>0.35823335657442523</v>
+        <v>0.016829755006852194</v>
       </c>
       <c r="E29" s="0">
-        <v>0.31922193382857633</v>
+        <v>0.048927473969987402</v>
       </c>
       <c r="F29" s="0">
-        <v>0.29472764981989003</v>
+        <v>0.0054579194411090749</v>
       </c>
       <c r="G29" s="0">
-        <v>1.0259505129752613</v>
+        <v>0</v>
       </c>
       <c r="H29" s="0">
-        <v>1.3293188661023752</v>
+        <v>0.01136169971027671</v>
       </c>
       <c r="I29" s="0">
-        <v>0.69909237155171033</v>
+        <v>0.06951202558042574</v>
       </c>
       <c r="J29" s="0">
-        <v>1.3617960986382103</v>
+        <v>0</v>
       </c>
       <c r="K29" s="0">
-        <v>0.77319587628866338</v>
+        <v>0.1288659793814439</v>
       </c>
       <c r="L29" s="0">
-        <v>0.069977918079184229</v>
+        <v>0.071532982925388316</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="0">
-        <v>0.70394801614649927</v>
+        <v>0.0073840700994388039</v>
       </c>
       <c r="B30" s="0">
-        <v>4.9122807017543817</v>
+        <v>0.26315789473684187</v>
       </c>
       <c r="C30" s="0">
-        <v>0.59726854258867035</v>
+        <v>0.11032348875841681</v>
       </c>
       <c r="D30" s="0">
-        <v>0.66838169884355481</v>
+        <v>0.074531772173202157</v>
       </c>
       <c r="E30" s="0">
-        <v>0.57340612786777601</v>
+        <v>0.12589874399594248</v>
       </c>
       <c r="F30" s="0">
-        <v>0.50212858858203213</v>
+        <v>0.01273514536258777</v>
       </c>
       <c r="G30" s="0">
-        <v>1.7501508750754358</v>
+        <v>0.020116676725005011</v>
       </c>
       <c r="H30" s="0">
-        <v>2.0905527466909031</v>
+        <v>0.005680849855138323</v>
       </c>
       <c r="I30" s="0">
-        <v>1.2909376179221852</v>
+        <v>0.16682886139302086</v>
       </c>
       <c r="J30" s="0">
-        <v>1.8586676481413307</v>
+        <v>0.092013249907986677</v>
       </c>
       <c r="K30" s="0">
-        <v>2.7061855670103068</v>
+        <v>0.38659793814432958</v>
       </c>
       <c r="L30" s="0">
-        <v>0.15861661431281671</v>
+        <v>0.17416726277485756</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="0">
-        <v>1.3709756817958048</v>
+        <v>0.017229496898690543</v>
       </c>
       <c r="B31" s="0">
-        <v>5.7894736842105212</v>
+        <v>0.61403508771929771</v>
       </c>
       <c r="C31" s="0">
-        <v>1.0778731660305092</v>
+        <v>0.26376190415805401</v>
       </c>
       <c r="D31" s="0">
-        <v>1.3006996369581407</v>
+        <v>0.18993580650590228</v>
       </c>
       <c r="E31" s="0">
-        <v>1.0215101882514386</v>
+        <v>0.24881410543273944</v>
       </c>
       <c r="F31" s="0">
-        <v>0.87144780409707745</v>
+        <v>0.0291089036859149</v>
       </c>
       <c r="G31" s="0">
-        <v>2.8364514182257068</v>
+        <v>0.080466706900020044</v>
       </c>
       <c r="H31" s="0">
-        <v>2.8631483269897151</v>
+        <v>0.073851048116798199</v>
       </c>
       <c r="I31" s="0">
-        <v>1.9681833528629007</v>
+        <v>0.35550435939703251</v>
       </c>
       <c r="J31" s="0">
-        <v>3.2388663967611309</v>
+        <v>0.25763709974236265</v>
       </c>
       <c r="K31" s="0">
-        <v>3.3505154639175228</v>
+        <v>0.64432989690721587</v>
       </c>
       <c r="L31" s="0">
-        <v>0.31412309893322521</v>
+        <v>0.38410101701240906</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="0">
-        <v>1.9370877227527796</v>
+        <v>0.066456630894949242</v>
       </c>
       <c r="B32" s="0">
-        <v>5.7894736842105212</v>
+        <v>1.7543859649122791</v>
       </c>
       <c r="C32" s="0">
-        <v>1.7030396023282044</v>
+        <v>0.50977060322854673</v>
       </c>
       <c r="D32" s="0">
-        <v>2.2119106580434189</v>
+        <v>0.32457384656071908</v>
       </c>
       <c r="E32" s="0">
-        <v>1.6313135833407904</v>
+        <v>0.51791521226766868</v>
       </c>
       <c r="F32" s="0">
-        <v>1.4136011352472424</v>
+        <v>0.069133646254047887</v>
       </c>
       <c r="G32" s="0">
-        <v>3.6411184872259073</v>
+        <v>0.10058338362502504</v>
       </c>
       <c r="H32" s="0">
-        <v>3.5789354087371441</v>
+        <v>0.22723399420553292</v>
       </c>
       <c r="I32" s="0">
-        <v>2.8460209330499868</v>
+        <v>0.75072987626859378</v>
       </c>
       <c r="J32" s="0">
-        <v>3.8093485461906482</v>
+        <v>0.25763709974236265</v>
       </c>
       <c r="K32" s="0">
-        <v>4.7680412371133976</v>
+        <v>1.1597938144329887</v>
       </c>
       <c r="L32" s="0">
-        <v>0.60181009548098108</v>
+        <v>0.71688489410008338</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="0">
-        <v>2.6459584522989048</v>
+        <v>0.14275868858915022</v>
       </c>
       <c r="B33" s="0">
-        <v>5.6140350877192935</v>
+        <v>1.9298245614035072</v>
       </c>
       <c r="C33" s="0">
-        <v>2.5868955984732218</v>
+        <v>0.91682623416477438</v>
       </c>
       <c r="D33" s="0">
-        <v>3.301036232058276</v>
+        <v>0.65155194383670267</v>
       </c>
       <c r="E33" s="0">
-        <v>2.2649840389033065</v>
+        <v>0.89262806169635056</v>
       </c>
       <c r="F33" s="0">
-        <v>2.044900483935522</v>
+        <v>0.21831677764436178</v>
       </c>
       <c r="G33" s="0">
-        <v>4.2043854355260475</v>
+        <v>0.16093341380004009</v>
       </c>
       <c r="H33" s="0">
-        <v>4.289041640629434</v>
+        <v>0.49991478725217248</v>
       </c>
       <c r="I33" s="0">
-        <v>3.517308494369523</v>
+        <v>1.3107981966594495</v>
       </c>
       <c r="J33" s="0">
-        <v>4.6374677953625278</v>
+        <v>0.80971659919028272</v>
       </c>
       <c r="K33" s="0">
-        <v>7.6030927835051472</v>
+        <v>2.4484536082474207</v>
       </c>
       <c r="L33" s="0">
-        <v>1.1025409759586966</v>
+        <v>1.3078095356576358</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="0">
-        <v>3.2588362705523251</v>
+        <v>0.33720586787437201</v>
       </c>
       <c r="B34" s="0">
-        <v>7.0175438596491162</v>
+        <v>4.8245614035087669</v>
       </c>
       <c r="C34" s="0">
-        <v>3.3870579134911645</v>
+        <v>1.5838395110260071</v>
       </c>
       <c r="D34" s="0">
-        <v>4.5127785925516273</v>
+        <v>1.334359146971845</v>
       </c>
       <c r="E34" s="0">
-        <v>2.9272949670336201</v>
+        <v>1.4003997732629243</v>
       </c>
       <c r="F34" s="0">
-        <v>2.9509151111596235</v>
+        <v>0.39478950624022091</v>
       </c>
       <c r="G34" s="0">
-        <v>4.9285857976262282</v>
+        <v>0.74431703882518541</v>
       </c>
       <c r="H34" s="0">
-        <v>4.3856160881667856</v>
+        <v>0.96006362551837676</v>
       </c>
       <c r="I34" s="0">
-        <v>4.2739965442592958</v>
+        <v>2.0019463367162502</v>
       </c>
       <c r="J34" s="0">
-        <v>4.8767022451232931</v>
+        <v>1.2881854987118135</v>
       </c>
       <c r="K34" s="0">
-        <v>10.051546391752568</v>
+        <v>3.7371134020618522</v>
       </c>
       <c r="L34" s="0">
-        <v>1.8318663888284126</v>
+        <v>1.9282804092930657</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="0">
-        <v>3.6526533425224152</v>
+        <v>0.61533917495323709</v>
       </c>
       <c r="B35" s="0">
-        <v>6.1403508771930104</v>
+        <v>6.4912280701754686</v>
       </c>
       <c r="C35" s="0">
-        <v>3.9729136813807107</v>
+        <v>2.2635336486640818</v>
       </c>
       <c r="D35" s="0">
-        <v>5.0994157670762146</v>
+        <v>2.2071021566129017</v>
       </c>
       <c r="E35" s="0">
-        <v>3.4159730302216813</v>
+        <v>2.0859810853545846</v>
       </c>
       <c r="F35" s="0">
-        <v>3.5913109922497708</v>
+        <v>0.69679438198159183</v>
       </c>
       <c r="G35" s="0">
-        <v>4.3854355260511166</v>
+        <v>1.1667672500502973</v>
       </c>
       <c r="H35" s="0">
-        <v>4.2663182412089045</v>
+        <v>1.5395103107424943</v>
       </c>
       <c r="I35" s="0">
-        <v>4.7764691863121111</v>
+        <v>2.8698536275347197</v>
       </c>
       <c r="J35" s="0">
-        <v>4.9135075450865155</v>
+        <v>2.245123297754887</v>
       </c>
       <c r="K35" s="0">
-        <v>11.082474226804175</v>
+        <v>6.185567010309307</v>
       </c>
       <c r="L35" s="0">
-        <v>2.6202842658538983</v>
+        <v>2.7726806207818995</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="0">
-        <v>3.896327655803876</v>
+        <v>1.1223786551146981</v>
       </c>
       <c r="B36" s="0">
-        <v>6.0526315789473628</v>
+        <v>5.7017543859649065</v>
       </c>
       <c r="C36" s="0">
-        <v>4.51058217831826</v>
+        <v>3.1321726118768911</v>
       </c>
       <c r="D36" s="0">
-        <v>5.9745630274324952</v>
+        <v>3.3731637535162138</v>
       </c>
       <c r="E36" s="0">
-        <v>3.6409200751812376</v>
+        <v>2.6522270950803999</v>
       </c>
       <c r="F36" s="0">
-        <v>3.9988356438525599</v>
+        <v>1.2098388094458381</v>
       </c>
       <c r="G36" s="0">
-        <v>4.5664856165761378</v>
+        <v>1.8708509354254659</v>
       </c>
       <c r="H36" s="0">
-        <v>3.9254672499005814</v>
+        <v>2.4314037379992026</v>
       </c>
       <c r="I36" s="0">
-        <v>4.9651446843160967</v>
+        <v>3.7318027447319784</v>
       </c>
       <c r="J36" s="0">
-        <v>4.5638571954361389</v>
+        <v>3.1284504968715465</v>
       </c>
       <c r="K36" s="0">
-        <v>10.180412371134011</v>
+        <v>7.2164948453608178</v>
       </c>
       <c r="L36" s="0">
-        <v>3.3464995490311917</v>
+        <v>3.5968649892700491</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="0">
-        <v>3.7068031899182792</v>
+        <v>1.7278724032686803</v>
       </c>
       <c r="B37" s="0">
-        <v>3.8596491228070144</v>
+        <v>6.578947368421046</v>
       </c>
       <c r="C37" s="0">
-        <v>4.5080460061628944</v>
+        <v>3.8220114381364167</v>
       </c>
       <c r="D37" s="0">
-        <v>5.7245209530449781</v>
+        <v>4.3156300338999314</v>
       </c>
       <c r="E37" s="0">
-        <v>3.9392583310957927</v>
+        <v>3.3360183776365608</v>
       </c>
       <c r="F37" s="0">
-        <v>4.333588036240581</v>
+        <v>1.9666703052796257</v>
       </c>
       <c r="G37" s="0">
-        <v>4.1440354053510324</v>
+        <v>2.9169181251257266</v>
       </c>
       <c r="H37" s="0">
-        <v>3.6414247571436653</v>
+        <v>3.198318468442876</v>
       </c>
       <c r="I37" s="0">
-        <v>4.8181764016603399</v>
+        <v>4.3494667434609005</v>
       </c>
       <c r="J37" s="0">
-        <v>4.3614280456385677</v>
+        <v>4.1589988958409974</v>
       </c>
       <c r="K37" s="0">
         <v>10.180412371134011</v>
       </c>
       <c r="L37" s="0">
-        <v>3.9685254875128257</v>
+        <v>3.9856312008210706</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="0">
-        <v>3.7461848971152869</v>
+        <v>2.4810475534114382</v>
       </c>
       <c r="B38" s="0">
-        <v>2.368421052631577</v>
+        <v>6.6666666666666608</v>
       </c>
       <c r="C38" s="0">
-        <v>4.6944546595822878</v>
+        <v>4.3951863452491118</v>
       </c>
       <c r="D38" s="0">
-        <v>5.1931815449715053</v>
+        <v>5.2677133171447075</v>
       </c>
       <c r="E38" s="0">
-        <v>3.9106178585279956</v>
+        <v>3.6725439303081804</v>
       </c>
       <c r="F38" s="0">
-        <v>4.3936251500927801</v>
+        <v>2.6361750900556684</v>
       </c>
       <c r="G38" s="0">
-        <v>3.339368336350832</v>
+        <v>4.0032186682759967</v>
       </c>
       <c r="H38" s="0">
-        <v>2.9540419246719285</v>
+        <v>4.1527012441061144</v>
       </c>
       <c r="I38" s="0">
-        <v>4.6573057138884986</v>
+        <v>4.8102321701654338</v>
       </c>
       <c r="J38" s="0">
-        <v>2.9812292970187682</v>
+        <v>4.8951048951048906</v>
       </c>
       <c r="K38" s="0">
-        <v>9.7938144329896826</v>
+        <v>11.340206185567</v>
       </c>
       <c r="L38" s="0">
-        <v>4.1846795011351938</v>
+        <v>4.3308555966783784</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="0">
-        <v>3.5246627941321229</v>
+        <v>3.0496209510682259</v>
       </c>
       <c r="B39" s="0">
-        <v>2.2807017543859631</v>
+        <v>6.7543859649122746</v>
       </c>
       <c r="C39" s="0">
-        <v>4.2544287906263039</v>
+        <v>4.5055098340075288</v>
       </c>
       <c r="D39" s="0">
-        <v>4.714735652633852</v>
+        <v>5.8639674945303248</v>
       </c>
       <c r="E39" s="0">
-        <v>3.7274381693964584</v>
+        <v>3.9332915659775014</v>
       </c>
       <c r="F39" s="0">
-        <v>4.102536113233632</v>
+        <v>3.3147764072335599</v>
       </c>
       <c r="G39" s="0">
-        <v>3.0175015087507515</v>
+        <v>4.2043854355260475</v>
       </c>
       <c r="H39" s="0">
-        <v>2.6586377322047356</v>
+        <v>4.3458501391808175</v>
       </c>
       <c r="I39" s="0">
-        <v>4.4467835792734958</v>
+        <v>4.8857023693670394</v>
       </c>
       <c r="J39" s="0">
-        <v>2.6131762973868211</v>
+        <v>4.6374677953625279</v>
       </c>
       <c r="K39" s="0">
-        <v>4.8969072164948413</v>
+        <v>11.469072164948443</v>
       </c>
       <c r="L39" s="0">
-        <v>4.1566883339035199</v>
+        <v>4.2577675489067852</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="0">
-        <v>3.4335925962390439</v>
+        <v>3.6821896229201498</v>
       </c>
       <c r="B40" s="0">
-        <v>1.4912280701754372</v>
+        <v>5.0877192982456094</v>
       </c>
       <c r="C40" s="0">
-        <v>4.1796117120430099</v>
+        <v>4.7172802089805819</v>
       </c>
       <c r="D40" s="0">
-        <v>3.7025461015074619</v>
+        <v>5.765393215204476</v>
       </c>
       <c r="E40" s="0">
-        <v>3.6820907544974455</v>
+        <v>4.0114561890271156</v>
       </c>
       <c r="F40" s="0">
-        <v>3.9151475457555547</v>
+        <v>3.9679074336862756</v>
       </c>
       <c r="G40" s="0">
-        <v>2.7962180647756965</v>
+        <v>4.8078857372761972</v>
       </c>
       <c r="H40" s="0">
-        <v>2.4370845878543408</v>
+        <v>4.5560415838209361</v>
       </c>
       <c r="I40" s="0">
-        <v>3.9661575738316981</v>
+        <v>4.8539254433874159</v>
       </c>
       <c r="J40" s="0">
-        <v>2.5947736474052241</v>
+        <v>4.7846889952153067</v>
       </c>
       <c r="K40" s="0">
-        <v>3.8659793814432959</v>
+        <v>10.051546391752568</v>
       </c>
       <c r="L40" s="0">
-        <v>4.2810935215998471</v>
+        <v>4.2111156035206632</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="0">
-        <v>3.4877424436349478</v>
+        <v>3.8987890125037103</v>
       </c>
       <c r="B41" s="0">
-        <v>0.87719298245614441</v>
+        <v>3.15789473684212</v>
       </c>
       <c r="C41" s="0">
-        <v>3.8892200002536357</v>
+        <v>4.2848628564907187</v>
       </c>
       <c r="D41" s="0">
-        <v>3.3659510013704388</v>
+        <v>5.2172240521241804</v>
       </c>
       <c r="E41" s="0">
-        <v>3.5800590709746878</v>
+        <v>3.8724305617709538</v>
       </c>
       <c r="F41" s="0">
-        <v>3.782338172688589</v>
+        <v>4.260815777025817</v>
       </c>
       <c r="G41" s="0">
-        <v>2.7157513578756918</v>
+        <v>4.7877690605512191</v>
       </c>
       <c r="H41" s="0">
-        <v>2.4768505368403231</v>
+        <v>4.2549565414986281</v>
       </c>
       <c r="I41" s="0">
-        <v>3.7496772655955373</v>
+        <v>4.5997100355504577</v>
       </c>
       <c r="J41" s="0">
-        <v>2.1715126978284975</v>
+        <v>4.7662863452337358</v>
       </c>
       <c r="K41" s="0">
-        <v>1.4175257731958828</v>
+        <v>8.5051546391752986</v>
       </c>
       <c r="L41" s="0">
-        <v>4.0058470438217464</v>
+        <v>3.9140982178957042</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="0">
-        <v>3.2416067736536354</v>
+        <v>3.9184798661021918</v>
       </c>
       <c r="B42" s="0">
-        <v>0.78947368421052566</v>
+        <v>2.2807017543859631</v>
       </c>
       <c r="C42" s="0">
-        <v>3.7269049823101961</v>
+        <v>4.1364967854017891</v>
       </c>
       <c r="D42" s="0">
-        <v>2.9091433654701486</v>
+        <v>4.6642463876132956</v>
       </c>
       <c r="E42" s="0">
-        <v>3.3276649064709538</v>
+        <v>3.5937826307467371</v>
       </c>
       <c r="F42" s="0">
-        <v>3.5258159589564424</v>
+        <v>4.4281919732198043</v>
       </c>
       <c r="G42" s="0">
-        <v>3.0376181854757567</v>
+        <v>4.425668879501103</v>
       </c>
       <c r="H42" s="0">
-        <v>2.7381696301766718</v>
+        <v>3.8743396012043365</v>
       </c>
       <c r="I42" s="0">
-        <v>3.5828484042024948</v>
+        <v>4.2819407757542018</v>
       </c>
       <c r="J42" s="0">
-        <v>2.1715126978284855</v>
+        <v>4.0853882959146084</v>
       </c>
       <c r="K42" s="0">
-        <v>1.1597938144329887</v>
+        <v>3.479381443298966</v>
       </c>
       <c r="L42" s="0">
-        <v>3.750816409044254</v>
+        <v>3.7648119926600909</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="0">
-        <v>3.2391454169538223</v>
+        <v>3.5985034951265105</v>
       </c>
       <c r="B43" s="0">
-        <v>0.70175438596491169</v>
+        <v>2.4561403508771908</v>
       </c>
       <c r="C43" s="0">
-        <v>3.5506410175122656</v>
+        <v>3.8397646432239787</v>
       </c>
       <c r="D43" s="0">
-        <v>2.8682711033106507</v>
+        <v>3.7193758565143145</v>
       </c>
       <c r="E43" s="0">
-        <v>3.2602404606342641</v>
+        <v>3.56514215817894</v>
       </c>
       <c r="F43" s="0">
-        <v>3.2347269220972938</v>
+        <v>4.0952588873121529</v>
       </c>
       <c r="G43" s="0">
-        <v>2.9973848320257468</v>
+        <v>4.043452021726007</v>
       </c>
       <c r="H43" s="0">
-        <v>2.9369993751065131</v>
+        <v>3.2324035675737064</v>
       </c>
       <c r="I43" s="0">
-        <v>3.3365772278604169</v>
+        <v>4.0555301781493878</v>
       </c>
       <c r="J43" s="0">
-        <v>2.5763709974236271</v>
+        <v>2.9628266470371707</v>
       </c>
       <c r="K43" s="0">
-        <v>0.77319587628865916</v>
+        <v>3.3505154639175228</v>
       </c>
       <c r="L43" s="0">
-        <v>3.5984200541162537</v>
+        <v>3.6559574534258048</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="0">
-        <v>3.2022250664566276</v>
+        <v>3.5738899281283811</v>
       </c>
       <c r="B44" s="0">
-        <v>0.35087719298245584</v>
+        <v>1.8421052631578929</v>
       </c>
       <c r="C44" s="0">
-        <v>3.294487629820309</v>
+        <v>3.8296199546025154</v>
       </c>
       <c r="D44" s="0">
-        <v>2.9668453826364987</v>
+        <v>3.3058447334888053</v>
       </c>
       <c r="E44" s="0">
-        <v>3.1653688952534358</v>
+        <v>3.4255198544109282</v>
       </c>
       <c r="F44" s="0">
-        <v>3.096459629589198</v>
+        <v>3.9187861587162942</v>
       </c>
       <c r="G44" s="0">
-        <v>3.2991349829008216</v>
+        <v>3.4600683967008616</v>
       </c>
       <c r="H44" s="0">
-        <v>2.9085951258308214</v>
+        <v>2.8574674771345769</v>
       </c>
       <c r="I44" s="0">
-        <v>3.1498877877301314</v>
+        <v>3.7695378443327807</v>
       </c>
       <c r="J44" s="0">
-        <v>2.7972027972027949</v>
+        <v>2.5395656974604321</v>
       </c>
       <c r="K44" s="0">
-        <v>0.12886597938144317</v>
+        <v>1.8041237113402044</v>
       </c>
       <c r="L44" s="0">
-        <v>3.5097813578826202</v>
+        <v>3.4677946070351107</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="0">
-        <v>2.8797873387811337</v>
+        <v>3.3474451117455915</v>
       </c>
       <c r="B45" s="0">
-        <v>0.43859649122806976</v>
+        <v>0.61403508771929771</v>
       </c>
       <c r="C45" s="0">
-        <v>2.9876107990210348</v>
+        <v>3.530351640269338</v>
       </c>
       <c r="D45" s="0">
-        <v>3.4380785228283575</v>
+        <v>3.0245473998028487</v>
       </c>
       <c r="E45" s="0">
-        <v>3.050807004982246</v>
+        <v>3.322891494376321</v>
       </c>
       <c r="F45" s="0">
-        <v>2.8490339482589211</v>
+        <v>3.8623876578248342</v>
       </c>
       <c r="G45" s="0">
-        <v>2.6352846509756565</v>
+        <v>2.8968014484007214</v>
       </c>
       <c r="H45" s="0">
-        <v>3.0335738226438647</v>
+        <v>2.3859569391580959</v>
       </c>
       <c r="I45" s="0">
-        <v>2.9790868105896577</v>
+        <v>3.4418382951679183</v>
       </c>
       <c r="J45" s="0">
-        <v>3.1652557968347415</v>
+        <v>2.1715126978284855</v>
       </c>
       <c r="K45" s="0">
-        <v>0.12886597938144317</v>
+        <v>1.0309278350515454</v>
       </c>
       <c r="L45" s="0">
-        <v>3.4102572077255591</v>
+        <v>3.3153982521071099</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="0">
-        <v>2.7394900068917964</v>
+        <v>3.4975878704341801</v>
       </c>
       <c r="B46" s="0">
-        <v>0.17543859649122792</v>
+        <v>0.52631578947368374</v>
       </c>
       <c r="C46" s="0">
-        <v>2.8354404696990807</v>
+        <v>3.4682154224628734</v>
       </c>
       <c r="D46" s="0">
-        <v>3.5005890414252372</v>
+        <v>2.7817180775611257</v>
       </c>
       <c r="E46" s="0">
-        <v>2.8998478474894811</v>
+        <v>3.114651391747961</v>
       </c>
       <c r="F46" s="0">
-        <v>2.9017938361896416</v>
+        <v>3.6731797838663867</v>
       </c>
       <c r="G46" s="0">
-        <v>2.9571514785757369</v>
+        <v>2.9772681553007416</v>
       </c>
       <c r="H46" s="0">
-        <v>2.7381696301766718</v>
+        <v>2.5279781855365542</v>
       </c>
       <c r="I46" s="0">
-        <v>2.7685646759746554</v>
+        <v>3.4934757998848052</v>
       </c>
       <c r="J46" s="0">
-        <v>2.5579683474420296</v>
+        <v>2.2267206477732771</v>
       </c>
       <c r="K46" s="0">
-        <v>0.12886597938144317</v>
+        <v>0.5154639175257727</v>
       </c>
       <c r="L46" s="0">
-        <v>3.21276397225764</v>
+        <v>3.2080987777190284</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="0">
-        <v>2.7542581470906895</v>
+        <v>3.298217977749351</v>
       </c>
       <c r="B47" s="0">
-        <v>0.61403508771930115</v>
+        <v>1.0526315789473733</v>
       </c>
       <c r="C47" s="0">
-        <v>2.7809127683587294</v>
+        <v>3.1207598371777623</v>
       </c>
       <c r="D47" s="0">
-        <v>3.2649724713293256</v>
+        <v>3.0173346476570719</v>
       </c>
       <c r="E47" s="0">
-        <v>2.8831409051582821</v>
+        <v>3.1039112145350543</v>
       </c>
       <c r="F47" s="0">
-        <v>2.6143434122912468</v>
+        <v>3.2893061165084023</v>
       </c>
       <c r="G47" s="0">
-        <v>2.1726010863005532</v>
+        <v>2.5145845906256401</v>
       </c>
       <c r="H47" s="0">
-        <v>2.6245526330739204</v>
+        <v>2.6756802817701653</v>
       </c>
       <c r="I47" s="0">
-        <v>2.6354987984349987</v>
+        <v>3.1061945145081671</v>
       </c>
       <c r="J47" s="0">
-        <v>3.0548398969451744</v>
+        <v>2.7235921972764205</v>
       </c>
       <c r="K47" s="0">
         <v>0.1288659793814439</v>
       </c>
       <c r="L47" s="0">
-        <v>3.0852486548689222</v>
+        <v>3.0074954125587179</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="0">
-        <v>2.6951855862951635</v>
+        <v>3.3597518952446559</v>
       </c>
       <c r="B48" s="0">
-        <v>1.4035087719298234</v>
+        <v>0.43859649122806976</v>
       </c>
       <c r="C48" s="0">
-        <v>2.6629807631341991</v>
+        <v>3.0459427585944505</v>
       </c>
       <c r="D48" s="0">
-        <v>3.2048662034476925</v>
+        <v>3.3322914913567159</v>
       </c>
       <c r="E48" s="0">
-        <v>2.7244249530117224</v>
+        <v>2.9278916435454492</v>
       </c>
       <c r="F48" s="0">
-        <v>2.4469672160972213</v>
+        <v>3.1201106138340036</v>
       </c>
       <c r="G48" s="0">
-        <v>2.152484409575536</v>
+        <v>2.8968014484007214</v>
       </c>
       <c r="H48" s="0">
-        <v>2.2155314435039464</v>
+        <v>2.7779355791626403</v>
       </c>
       <c r="I48" s="0">
-        <v>2.558042541359653</v>
+        <v>2.9274493058727704</v>
       </c>
       <c r="J48" s="0">
-        <v>2.3187338976812639</v>
+        <v>3.0180345969819626</v>
       </c>
       <c r="K48" s="0">
-        <v>0</v>
+        <v>0.12886597938144317</v>
       </c>
       <c r="L48" s="0">
-        <v>2.9452928187105378</v>
+        <v>2.7960065934749454</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="0">
-        <v>2.53273604410751</v>
+        <v>3.1480752190607433</v>
       </c>
       <c r="B49" s="0">
-        <v>1.3157894736842093</v>
+        <v>0.43859649122806976</v>
       </c>
       <c r="C49" s="0">
-        <v>2.4930572287246839</v>
+        <v>2.7783765962033478</v>
       </c>
       <c r="D49" s="0">
-        <v>2.8562498497343278</v>
+        <v>3.5606953093068512</v>
       </c>
       <c r="E49" s="0">
-        <v>2.6546138011277161</v>
+        <v>2.9076046421432595</v>
       </c>
       <c r="F49" s="0">
-        <v>2.3541825855983678</v>
+        <v>3.0200487574136714</v>
       </c>
       <c r="G49" s="0">
-        <v>2.0317843492255059</v>
+        <v>3.560651780325887</v>
       </c>
       <c r="H49" s="0">
-        <v>2.0621484974152113</v>
+        <v>2.8688291768448533</v>
       </c>
       <c r="I49" s="0">
-        <v>2.2323290500685169</v>
+        <v>2.8400627594288075</v>
       </c>
       <c r="J49" s="0">
-        <v>2.0426941479573042</v>
+        <v>2.8708133971291843</v>
       </c>
       <c r="K49" s="0">
-        <v>0</v>
+        <v>0.12886597938144317</v>
       </c>
       <c r="L49" s="0">
-        <v>2.7104780269337208</v>
+        <v>2.6436102385469451</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="0">
-        <v>2.5844245348035817</v>
+        <v>2.9930097469725285</v>
       </c>
       <c r="B50" s="0">
-        <v>2.7192982456140329</v>
+        <v>0.35087719298245584</v>
       </c>
       <c r="C50" s="0">
-        <v>2.3852699121216325</v>
+        <v>2.6008445453277345</v>
       </c>
       <c r="D50" s="0">
-        <v>2.3513571995287648</v>
+        <v>3.3515254970788324</v>
       </c>
       <c r="E50" s="0">
-        <v>2.5406485873683562</v>
+        <v>2.7584355141859818</v>
       </c>
       <c r="F50" s="0">
-        <v>2.517920168831639</v>
+        <v>2.8035512862496792</v>
       </c>
       <c r="G50" s="0">
-        <v>1.9312009656004812</v>
+        <v>2.8163347415007016</v>
       </c>
       <c r="H50" s="0">
-        <v>1.6588081577003906</v>
+        <v>3.1812759188774611</v>
       </c>
       <c r="I50" s="0">
-        <v>2.2502035709320549</v>
+        <v>2.5322237890012089</v>
       </c>
       <c r="J50" s="0">
-        <v>1.9138755980861226</v>
+        <v>2.8524107471475868</v>
       </c>
       <c r="K50" s="0">
-        <v>0</v>
+        <v>0.12886597938144317</v>
       </c>
       <c r="L50" s="0">
-        <v>2.6280595900849044</v>
+        <v>2.5378658290050673</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="0">
-        <v>2.488431623510877</v>
+        <v>2.727183223392732</v>
       </c>
       <c r="B51" s="0">
-        <v>3.2456140350877161</v>
+        <v>0.52631578947368374</v>
       </c>
       <c r="C51" s="0">
-        <v>2.3472273297911439</v>
+        <v>2.6680531074449307</v>
       </c>
       <c r="D51" s="0">
-        <v>2.0027408458153997</v>
+        <v>3.195249200586634</v>
       </c>
       <c r="E51" s="0">
-        <v>2.4606939347832553</v>
+        <v>2.6498403890330833</v>
       </c>
       <c r="F51" s="0">
-        <v>2.077648000582176</v>
+        <v>2.7908161408870913</v>
       </c>
       <c r="G51" s="0">
-        <v>1.9714343190504913</v>
+        <v>3.0778515389257666</v>
       </c>
       <c r="H51" s="0">
-        <v>1.7781060046582953</v>
+        <v>2.8461057774243002</v>
       </c>
       <c r="I51" s="0">
-        <v>2.0237929733272408</v>
+        <v>2.426962721693708</v>
       </c>
       <c r="J51" s="0">
-        <v>1.5274199484725786</v>
+        <v>2.5395656974604321</v>
       </c>
       <c r="K51" s="0">
         <v>0</v>
       </c>
       <c r="L51" s="0">
-        <v>2.4881037539265365</v>
+        <v>2.3201567505364955</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="0">
-        <v>2.3358275081224749</v>
+        <v>2.7197991532932928</v>
       </c>
       <c r="B52" s="0">
-        <v>3.1578947368421026</v>
+        <v>1.7543859649122791</v>
       </c>
       <c r="C52" s="0">
-        <v>2.1392612130511401</v>
+        <v>2.4410656995396827</v>
       </c>
       <c r="D52" s="0">
-        <v>1.7334647657057662</v>
+        <v>2.716803308248982</v>
       </c>
       <c r="E52" s="0">
-        <v>2.3306184552045086</v>
+        <v>2.5072347027059259</v>
       </c>
       <c r="F52" s="0">
-        <v>2.2523014226976659</v>
+        <v>2.563402830840881</v>
       </c>
       <c r="G52" s="0">
-        <v>1.7099175216254261</v>
+        <v>2.5548179440756362</v>
       </c>
       <c r="H52" s="0">
-        <v>2.0167016985741051</v>
+        <v>2.5734249843776604</v>
       </c>
       <c r="I52" s="0">
-        <v>1.9086016166511073</v>
+        <v>2.3971718535878117</v>
       </c>
       <c r="J52" s="0">
-        <v>1.3986013986013974</v>
+        <v>2.4107471475892508</v>
       </c>
       <c r="K52" s="0">
-        <v>0.12886597938144317</v>
+        <v>0</v>
       </c>
       <c r="L52" s="0">
-        <v>2.2828351942275975</v>
+        <v>2.315491555997883</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="0">
-        <v>2.1881461061336989</v>
+        <v>2.6779560893964729</v>
       </c>
       <c r="B53" s="0">
-        <v>3.6842105263157858</v>
+        <v>1.2280701754385954</v>
       </c>
       <c r="C53" s="0">
-        <v>2.0581037040794312</v>
+        <v>2.2952358006061431</v>
       </c>
       <c r="D53" s="0">
-        <v>1.6012309763662138</v>
+        <v>2.5292717524583441</v>
       </c>
       <c r="E53" s="0">
-        <v>2.2643873623914774</v>
+        <v>2.4803842596736159</v>
       </c>
       <c r="F53" s="0">
-        <v>2.1067569042680909</v>
+        <v>2.437870683695373</v>
       </c>
       <c r="G53" s="0">
-        <v>1.9513176423254861</v>
+        <v>1.911084288875476</v>
       </c>
       <c r="H53" s="0">
-        <v>2.2041697437936696</v>
+        <v>2.2439356927796381</v>
       </c>
       <c r="I53" s="0">
-        <v>1.7695775654902568</v>
+        <v>2.285952612659131</v>
       </c>
       <c r="J53" s="0">
-        <v>1.4722119985277868</v>
+        <v>1.9506808980493173</v>
       </c>
       <c r="K53" s="0">
-        <v>0.12886597938144317</v>
+        <v>0</v>
       </c>
       <c r="L53" s="0">
-        <v>2.1319939041458009</v>
+        <v>2.2501788324573115</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="0">
-        <v>2.1659938958353826</v>
+        <v>2.5475041843063875</v>
       </c>
       <c r="B54" s="0">
-        <v>3.5964912280701724</v>
+        <v>2.368421052631577</v>
       </c>
       <c r="C54" s="0">
-        <v>1.926222752000404</v>
+        <v>2.1417973852065058</v>
       </c>
       <c r="D54" s="0">
-        <v>1.8079965378789684</v>
+        <v>2.0195706008222518</v>
       </c>
       <c r="E54" s="0">
-        <v>2.219636624004294</v>
+        <v>2.3520988096303568</v>
       </c>
       <c r="F54" s="0">
-        <v>1.8265837062911601</v>
+        <v>2.3378088272750408</v>
       </c>
       <c r="G54" s="0">
-        <v>2.1726010863005412</v>
+        <v>2.0317843492255059</v>
       </c>
       <c r="H54" s="0">
-        <v>2.0110208487189665</v>
+        <v>1.9826165994432752</v>
       </c>
       <c r="I54" s="0">
-        <v>1.7040376556572845</v>
+        <v>2.1151516355186573</v>
       </c>
       <c r="J54" s="0">
-        <v>2.0242914979757067</v>
+        <v>2.0610967979389012</v>
       </c>
       <c r="K54" s="0">
         <v>0.12886597938144317</v>
       </c>
       <c r="L54" s="0">
-        <v>1.9920380679874332</v>
+        <v>2.0215843000653111</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="0">
-        <v>1.9838535000492252</v>
+        <v>2.5647336812050781</v>
       </c>
       <c r="B55" s="0">
-        <v>2.9824561403508745</v>
+        <v>3.1578947368421026</v>
       </c>
       <c r="C55" s="0">
-        <v>1.799414144232109</v>
+        <v>2.1177037497305298</v>
       </c>
       <c r="D55" s="0">
-        <v>1.9306133243574621</v>
+        <v>1.7382732671362955</v>
       </c>
       <c r="E55" s="0">
-        <v>2.1480354425848009</v>
+        <v>2.2912378054237874</v>
       </c>
       <c r="F55" s="0">
-        <v>1.9230069497507534</v>
+        <v>2.2577593421387747</v>
       </c>
       <c r="G55" s="0">
-        <v>1.6294508147254059</v>
+        <v>2.1122510561255261</v>
       </c>
       <c r="H55" s="0">
-        <v>1.9144464011816149</v>
+        <v>1.8576379026302319</v>
       </c>
       <c r="I55" s="0">
-        <v>1.6464419773192178</v>
+        <v>1.8728525749240317</v>
       </c>
       <c r="J55" s="0">
-        <v>1.821862348178136</v>
+        <v>1.5274199484725786</v>
       </c>
       <c r="K55" s="0">
-        <v>0.5154639175257727</v>
+        <v>0</v>
       </c>
       <c r="L55" s="0">
-        <v>2.0371349485273518</v>
+        <v>1.9656019656019639</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="0">
-        <v>1.9395490794525925</v>
+        <v>2.4268977060155539</v>
       </c>
       <c r="B56" s="0">
-        <v>1.2280701754385954</v>
+        <v>2.8070175438596467</v>
       </c>
       <c r="C56" s="0">
-        <v>1.6928949137067411</v>
+        <v>1.9236865798450382</v>
       </c>
       <c r="D56" s="0">
-        <v>1.6300819849493893</v>
+        <v>1.6901882528310037</v>
       </c>
       <c r="E56" s="0">
-        <v>2.0895611444255482</v>
+        <v>2.2596139502968447</v>
       </c>
       <c r="F56" s="0">
-        <v>1.7428956081941549</v>
+        <v>2.2668558745406231</v>
       </c>
       <c r="G56" s="0">
-        <v>2.1122510561255261</v>
+        <v>1.8306175819754562</v>
       </c>
       <c r="H56" s="0">
-        <v>1.9542123501675834</v>
+        <v>1.738340055672327</v>
       </c>
       <c r="I56" s="0">
-        <v>1.5272785048956314</v>
+        <v>1.7636193918690777</v>
       </c>
       <c r="J56" s="0">
-        <v>2.0426941479573042</v>
+        <v>1.821862348178136</v>
       </c>
       <c r="K56" s="0">
-        <v>0.38659793814432958</v>
+        <v>0.25773195876288635</v>
       </c>
       <c r="L56" s="0">
-        <v>1.786769508288494</v>
+        <v>1.8614126209062902</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="0">
-        <v>1.9370877227528012</v>
+        <v>2.3875159988185732</v>
       </c>
       <c r="B57" s="0">
-        <v>1.4035087719298389</v>
+        <v>3.7719298245614419</v>
       </c>
       <c r="C57" s="0">
-        <v>1.7157204631050531</v>
+        <v>1.8602822759609112</v>
       </c>
       <c r="D57" s="0">
-        <v>1.687784002115758</v>
+        <v>1.6733584978241702</v>
       </c>
       <c r="E57" s="0">
-        <v>2.0060264327694948</v>
+        <v>2.1337152063009257</v>
       </c>
       <c r="F57" s="0">
-        <v>1.7665465924389803</v>
+        <v>2.0521777098570233</v>
       </c>
       <c r="G57" s="0">
-        <v>1.3478173405753506</v>
+        <v>1.9110842888754973</v>
       </c>
       <c r="H57" s="0">
-        <v>1.7553826052377617</v>
+        <v>2.084871896835788</v>
       </c>
       <c r="I57" s="0">
-        <v>1.3803102222398902</v>
+        <v>1.6623304403090475</v>
       </c>
       <c r="J57" s="0">
-        <v>1.6378358483621809</v>
+        <v>1.4906146485094007</v>
       </c>
       <c r="K57" s="0">
-        <v>0.77319587628866771</v>
+        <v>0</v>
       </c>
       <c r="L57" s="0">
-        <v>1.8691879451373312</v>
+        <v>1.772773924672677</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="0">
-        <v>1.8755538052574563</v>
+        <v>2.220143743231267</v>
       </c>
       <c r="B58" s="0">
-        <v>0.96491228070175361</v>
+        <v>3.2456140350877161</v>
       </c>
       <c r="C58" s="0">
-        <v>1.5597458755500311</v>
+        <v>1.8450652430286951</v>
       </c>
       <c r="D58" s="0">
-        <v>1.5459332099151286</v>
+        <v>1.7551030221431474</v>
       </c>
       <c r="E58" s="0">
-        <v>1.9081714848294979</v>
+        <v>2.0943345565201805</v>
       </c>
       <c r="F58" s="0">
-        <v>1.6555688971364102</v>
+        <v>1.9321034821526017</v>
       </c>
       <c r="G58" s="0">
-        <v>1.3277006638503308</v>
+        <v>1.9312009656004812</v>
       </c>
       <c r="H58" s="0">
-        <v>1.5111060614667942</v>
+        <v>2.0053399988638283</v>
       </c>
       <c r="I58" s="0">
-        <v>1.2869655021747322</v>
+        <v>1.5133760997795462</v>
       </c>
       <c r="J58" s="0">
-        <v>1.3065881486934106</v>
+        <v>1.8586676481413307</v>
       </c>
       <c r="K58" s="0">
-        <v>1.0309278350515454</v>
+        <v>0.5154639175257727</v>
       </c>
       <c r="L58" s="0">
-        <v>1.7696637949802489</v>
+        <v>1.6452586072839222</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="0">
-        <v>1.5629615043812133</v>
+        <v>2.1463030422368794</v>
       </c>
       <c r="B59" s="0">
-        <v>0.43859649122806976</v>
+        <v>2.9824561403508745</v>
       </c>
       <c r="C59" s="0">
-        <v>1.5001458298989323</v>
+        <v>1.6738736225414967</v>
       </c>
       <c r="D59" s="0">
-        <v>1.2862741326665532</v>
+        <v>1.6853797514004745</v>
       </c>
       <c r="E59" s="0">
-        <v>1.8079298308422074</v>
+        <v>1.9881261374145989</v>
       </c>
       <c r="F59" s="0">
-        <v>1.6155441545682772</v>
+        <v>1.8356802386930084</v>
       </c>
       <c r="G59" s="0">
-        <v>1.1064172198752757</v>
+        <v>2.3134178233755764</v>
       </c>
       <c r="H59" s="0">
-        <v>1.2497869681304312</v>
+        <v>2.1359995455320098</v>
       </c>
       <c r="I59" s="0">
-        <v>1.0963039462969941</v>
+        <v>1.5391948521379899</v>
       </c>
       <c r="J59" s="0">
-        <v>1.3801987486198</v>
+        <v>1.6930437983069548</v>
       </c>
       <c r="K59" s="0">
-        <v>0.64432989690721587</v>
+        <v>0.5154639175257727</v>
       </c>
       <c r="L59" s="0">
-        <v>1.6048269212826161</v>
+        <v>1.5954965322053916</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="0">
-        <v>1.4940435167864512</v>
+        <v>1.9567785763512831</v>
       </c>
       <c r="B60" s="0">
-        <v>0.35087719298245584</v>
+        <v>1.7543859649122791</v>
       </c>
       <c r="C60" s="0">
-        <v>1.4304010956263697</v>
+        <v>1.5724267363268607</v>
       </c>
       <c r="D60" s="0">
-        <v>1.1131680811675031</v>
+        <v>1.6637414949630931</v>
       </c>
       <c r="E60" s="0">
-        <v>1.6557773203257837</v>
+        <v>1.9463587815865613</v>
       </c>
       <c r="F60" s="0">
-        <v>1.5318560564712718</v>
+        <v>1.8374995451733782</v>
       </c>
       <c r="G60" s="0">
-        <v>1.1868839267752955</v>
+        <v>1.9513176423254861</v>
       </c>
       <c r="H60" s="0">
-        <v>1.3122763165369529</v>
+        <v>2.050786797704935</v>
       </c>
       <c r="I60" s="0">
-        <v>1.1340390458977965</v>
+        <v>1.3564775277551575</v>
       </c>
       <c r="J60" s="0">
-        <v>1.0489510489510481</v>
+        <v>1.987486198012512</v>
       </c>
       <c r="K60" s="0">
-        <v>0.64432989690721587</v>
+        <v>0.5154639175257727</v>
       </c>
       <c r="L60" s="0">
-        <v>1.4835318632786976</v>
+        <v>1.531738873511024</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="0">
-        <v>1.5211184404843936</v>
+        <v>2.1463030422368794</v>
       </c>
       <c r="B61" s="0">
-        <v>0.52631578947368374</v>
+        <v>1.0526315789473675</v>
       </c>
       <c r="C61" s="0">
-        <v>1.2452605282846587</v>
+        <v>1.4025032019173449</v>
       </c>
       <c r="D61" s="0">
-        <v>0.92082802394633634</v>
+        <v>1.5579544634914515</v>
       </c>
       <c r="E61" s="0">
-        <v>1.5967063456547019</v>
+        <v>1.8568573048121944</v>
       </c>
       <c r="F61" s="0">
-        <v>1.4481679583742664</v>
+        <v>1.7228832369100884</v>
       </c>
       <c r="G61" s="0">
-        <v>1.5288674311003809</v>
+        <v>1.7099175216254261</v>
       </c>
       <c r="H61" s="0">
-        <v>1.2384252684201547</v>
+        <v>1.9428506504573066</v>
       </c>
       <c r="I61" s="0">
-        <v>1.0406943258326538</v>
+        <v>1.2591606919425622</v>
       </c>
       <c r="J61" s="0">
-        <v>0.92013249907986661</v>
+        <v>2.0979020979020961</v>
       </c>
       <c r="K61" s="0">
-        <v>0.25773195876288635</v>
+        <v>0.5154639175257727</v>
       </c>
       <c r="L61" s="0">
-        <v>1.3637918701209828</v>
+        <v>1.4182191397381259</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="0">
-        <v>1.3660529683961788</v>
+        <v>1.9912375701486642</v>
       </c>
       <c r="B62" s="0">
-        <v>0</v>
+        <v>0.96491228070175361</v>
       </c>
       <c r="C62" s="0">
-        <v>1.2110222041872192</v>
+        <v>1.50775434636503</v>
       </c>
       <c r="D62" s="0">
-        <v>0.77416873031519662</v>
+        <v>1.3944654148534597</v>
       </c>
       <c r="E62" s="0">
-        <v>1.5066081923685062</v>
+        <v>1.7178316775560114</v>
       </c>
       <c r="F62" s="0">
-        <v>1.3662991667576307</v>
+        <v>1.730160462831567</v>
       </c>
       <c r="G62" s="0">
-        <v>1.4886340776503708</v>
+        <v>1.5489841078253859</v>
       </c>
       <c r="H62" s="0">
-        <v>1.0339146736351748</v>
+        <v>1.653127307845252</v>
       </c>
       <c r="I62" s="0">
-        <v>1.0406943258326538</v>
+        <v>1.1836904927409575</v>
       </c>
       <c r="J62" s="0">
-        <v>1.159366948840632</v>
+        <v>1.4722119985277868</v>
       </c>
       <c r="K62" s="0">
-        <v>0.12886597938144317</v>
+        <v>1.0309278350515454</v>
       </c>
       <c r="L62" s="0">
-        <v>1.3186949895810642</v>
+        <v>1.3995583615836766</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="0">
-        <v>1.3168258343999202</v>
+        <v>1.8337107413606364</v>
       </c>
       <c r="B63" s="0">
-        <v>0.17543859649122792</v>
+        <v>0.26315789473684187</v>
       </c>
       <c r="C63" s="0">
-        <v>1.0918221128850216</v>
+        <v>1.3264180372563679</v>
       </c>
       <c r="D63" s="0">
-        <v>0.71165821171831734</v>
+        <v>1.120380833313297</v>
       </c>
       <c r="E63" s="0">
-        <v>1.4415704525791329</v>
+        <v>1.6187833765923792</v>
       </c>
       <c r="F63" s="0">
-        <v>1.2753338427391465</v>
+        <v>1.6155441545682772</v>
       </c>
       <c r="G63" s="0">
-        <v>1.1868839267752955</v>
+        <v>1.3880506940253456</v>
       </c>
       <c r="H63" s="0">
-        <v>1.0907231721865582</v>
+        <v>1.5508720104527622</v>
       </c>
       <c r="I63" s="0">
-        <v>0.90961450616670891</v>
+        <v>1.054596730948739</v>
       </c>
       <c r="J63" s="0">
-        <v>1.1225616488774373</v>
+        <v>1.7298490982701495</v>
       </c>
       <c r="K63" s="0">
-        <v>0.38659793814432958</v>
+        <v>0.5154639175257727</v>
       </c>
       <c r="L63" s="0">
-        <v>1.3591266755823705</v>
+        <v>1.2844835629645746</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="0">
-        <v>1.2479078468051579</v>
+        <v>1.6884906960716732</v>
       </c>
       <c r="B64" s="0">
-        <v>0.26315789473684187</v>
+        <v>0.70175438596491169</v>
       </c>
       <c r="C64" s="0">
-        <v>1.1602987610799012</v>
+        <v>1.3099329182464894</v>
       </c>
       <c r="D64" s="0">
-        <v>0.70444545957252358</v>
+        <v>0.92804077609213009</v>
       </c>
       <c r="E64" s="0">
-        <v>1.3580357409230575</v>
+        <v>1.5078015453921643</v>
       </c>
       <c r="F64" s="0">
-        <v>1.2462249390532318</v>
+        <v>1.5536877342357081</v>
       </c>
       <c r="G64" s="0">
-        <v>1.1064172198752757</v>
+        <v>1.1265338966002805</v>
       </c>
       <c r="H64" s="0">
-        <v>1.2441061182752928</v>
+        <v>1.4372550133499957</v>
       </c>
       <c r="I64" s="0">
-        <v>0.95330777938869049</v>
+        <v>1.0307640364640216</v>
       </c>
       <c r="J64" s="0">
-        <v>1.0305483989694506</v>
+        <v>1.2145748987854241</v>
       </c>
       <c r="K64" s="0">
-        <v>0.25773195876288635</v>
+        <v>0.90206185567010222</v>
       </c>
       <c r="L64" s="0">
-        <v>1.2891487575031866</v>
+        <v>1.2627126551177173</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="0">
-        <v>1.0756128778182525</v>
+        <v>1.5752682878802782</v>
       </c>
       <c r="B65" s="0">
-        <v>0.17543859649122792</v>
+        <v>0.26315789473684187</v>
       </c>
       <c r="C65" s="0">
-        <v>1.0664603913313626</v>
+        <v>1.189464740866609</v>
       </c>
       <c r="D65" s="0">
-        <v>0.70204120885725907</v>
+        <v>0.80301973889837164</v>
       </c>
       <c r="E65" s="0">
-        <v>1.2375070855335768</v>
+        <v>1.4910946030609493</v>
       </c>
       <c r="F65" s="0">
-        <v>1.1607175344758569</v>
+        <v>1.4026852963650245</v>
       </c>
       <c r="G65" s="0">
-        <v>0.94548380607523552</v>
+        <v>1.0058338362502506</v>
       </c>
       <c r="H65" s="0">
-        <v>1.0339146736351748</v>
+        <v>1.1532125205930797</v>
       </c>
       <c r="I65" s="0">
-        <v>0.80435343885920763</v>
+        <v>0.99501499473694577</v>
       </c>
       <c r="J65" s="0">
-        <v>0.92013249907986661</v>
+        <v>1.3801987486198</v>
       </c>
       <c r="K65" s="0">
-        <v>0.12886597938144317</v>
+        <v>0.38659793814432958</v>
       </c>
       <c r="L65" s="0">
-        <v>1.2051752558081661</v>
+        <v>1.1460827916524108</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="0">
-        <v>1.0657674510190007</v>
+        <v>1.5580387909815876</v>
       </c>
       <c r="B66" s="0">
-        <v>0.43859649122806976</v>
+        <v>0.087719298245613961</v>
       </c>
       <c r="C66" s="0">
-        <v>0.96120924688367759</v>
+        <v>1.0829455103412409</v>
       </c>
       <c r="D66" s="0">
-        <v>0.70925396100305282</v>
+        <v>0.79340273603731315</v>
       </c>
       <c r="E66" s="0">
-        <v>1.142038843640919</v>
+        <v>1.3753393597661014</v>
       </c>
       <c r="F66" s="0">
-        <v>1.0442819197321971</v>
+        <v>1.3280937306698675</v>
       </c>
       <c r="G66" s="0">
-        <v>0.76443371555019046</v>
+        <v>1.2874673104003207</v>
       </c>
       <c r="H66" s="0">
-        <v>1.0679997727660049</v>
+        <v>1.2725103675509846</v>
       </c>
       <c r="I66" s="0">
-        <v>0.73086929753132945</v>
+        <v>0.9394053742726054</v>
       </c>
       <c r="J66" s="0">
-        <v>1.1777695988222294</v>
+        <v>0.84652189915347742</v>
       </c>
       <c r="K66" s="0">
-        <v>0</v>
+        <v>0.12886597938144317</v>
       </c>
       <c r="L66" s="0">
-        <v>1.1771840885764926</v>
+        <v>1.0869903274966555</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="0">
-        <v>0.99192675002461261</v>
+        <v>1.4128187456926245</v>
       </c>
       <c r="B67" s="0">
-        <v>0.52631578947368374</v>
+        <v>0.087719298245613961</v>
       </c>
       <c r="C67" s="0">
-        <v>0.95106455826221403</v>
+        <v>1.0182731203794104</v>
       </c>
       <c r="D67" s="0">
-        <v>0.60587118024667552</v>
+        <v>0.75974322602360911</v>
       </c>
       <c r="E67" s="0">
-        <v>1.0638742205913054</v>
+        <v>1.2619708225185704</v>
       </c>
       <c r="F67" s="0">
-        <v>0.96059382163519191</v>
+        <v>1.3008041334643223</v>
       </c>
       <c r="G67" s="0">
-        <v>0.76443371555019046</v>
+        <v>1.569100784550391</v>
       </c>
       <c r="H67" s="0">
-        <v>0.94870192580810009</v>
+        <v>1.2157018689996013</v>
       </c>
       <c r="I67" s="0">
-        <v>0.69313419793052711</v>
+        <v>0.90564239041925609</v>
       </c>
       <c r="J67" s="0">
-        <v>1.0489510489510481</v>
+        <v>1.10415899889584</v>
       </c>
       <c r="K67" s="0">
-        <v>0</v>
+        <v>0.12886597938144317</v>
       </c>
       <c r="L67" s="0">
-        <v>1.021677603956084</v>
+        <v>1.0325630578795126</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="0">
-        <v>0.87870434183321766</v>
+        <v>1.3439007580978624</v>
       </c>
       <c r="B68" s="0">
-        <v>0.70175438596491169</v>
+        <v>0.26315789473684187</v>
       </c>
       <c r="C68" s="0">
-        <v>0.89273259868879817</v>
+        <v>0.94599221395148225</v>
       </c>
       <c r="D68" s="0">
-        <v>0.60106267881614639</v>
+        <v>0.63472218882985065</v>
       </c>
       <c r="E68" s="0">
-        <v>0.9618425370685274</v>
+        <v>1.1665025806259126</v>
       </c>
       <c r="F68" s="0">
-        <v>1.038824000291088</v>
+        <v>1.2444056325728621</v>
       </c>
       <c r="G68" s="0">
-        <v>0.64373365520016035</v>
+        <v>1.3277006638503308</v>
       </c>
       <c r="H68" s="0">
-        <v>0.86917002783616348</v>
+        <v>1.2781912174061227</v>
       </c>
       <c r="I68" s="0">
-        <v>0.66532938769835692</v>
+        <v>0.81626978610156631</v>
       </c>
       <c r="J68" s="0">
-        <v>0.95693779904306131</v>
+        <v>1.159366948840632</v>
       </c>
       <c r="K68" s="0">
         <v>0</v>
       </c>
       <c r="L68" s="0">
-        <v>0.98902124218579834</v>
+        <v>1.003016825801635</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="0">
-        <v>0.90824062223098301</v>
+        <v>1.3685143250960068</v>
       </c>
       <c r="B69" s="0">
-        <v>0.52631578947368962</v>
+        <v>0.26315789473684481</v>
       </c>
       <c r="C69" s="0">
-        <v>0.825524036571611</v>
+        <v>0.9637454190390542</v>
       </c>
       <c r="D69" s="0">
-        <v>0.5265309066429501</v>
+        <v>0.663573197413033</v>
       </c>
       <c r="E69" s="0">
-        <v>0.8741310898296577</v>
+        <v>1.0573107789611971</v>
       </c>
       <c r="F69" s="0">
-        <v>0.88600225594004467</v>
+        <v>1.2243932612888091</v>
       </c>
       <c r="G69" s="0">
-        <v>0.52303359485013612</v>
+        <v>1.3075839871253403</v>
       </c>
       <c r="H69" s="0">
-        <v>0.8350849287053429</v>
+        <v>1.1134465716071238</v>
       </c>
       <c r="I69" s="0">
-        <v>0.57198466763322064</v>
+        <v>0.72093900816270529</v>
       </c>
       <c r="J69" s="0">
-        <v>0.90172984909827925</v>
+        <v>1.0305483989694622</v>
       </c>
       <c r="K69" s="0">
         <v>0</v>
       </c>
       <c r="L69" s="0">
-        <v>1.0014617609554421</v>
+        <v>0.94547942649209427</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="0">
-        <v>0.70148665944668642</v>
+        <v>1.1937579994092733</v>
       </c>
       <c r="B70" s="0">
-        <v>1.7543859649122791</v>
+        <v>0.52631578947368374</v>
       </c>
       <c r="C70" s="0">
-        <v>0.73802609721147805</v>
+        <v>0.88385599614501753</v>
       </c>
       <c r="D70" s="0">
-        <v>0.37265886086601074</v>
+        <v>0.5890414252398235</v>
       </c>
       <c r="E70" s="0">
-        <v>0.80312658492198374</v>
+        <v>1.0161400996449765</v>
       </c>
       <c r="F70" s="0">
-        <v>0.89146017538114386</v>
+        <v>1.1698140668777053</v>
       </c>
       <c r="G70" s="0">
-        <v>0.60350030175015035</v>
+        <v>1.0259505129752555</v>
       </c>
       <c r="H70" s="0">
-        <v>0.77259558029881203</v>
+        <v>1.1304891211725263</v>
       </c>
       <c r="I70" s="0">
-        <v>0.57794284125439366</v>
+        <v>0.71299477666779143</v>
       </c>
       <c r="J70" s="0">
-        <v>0.73610599926389342</v>
+        <v>0.79131394920868536</v>
       </c>
       <c r="K70" s="0">
         <v>0</v>
       </c>
       <c r="L70" s="0">
-        <v>0.92370851864522663</v>
+        <v>0.89260722172114493</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="0">
-        <v>0.73348429654425451</v>
+        <v>1.0042335335236774</v>
       </c>
       <c r="B71" s="0">
-        <v>0.87719298245613953</v>
+        <v>0.70175438596491169</v>
       </c>
       <c r="C71" s="0">
-        <v>0.69744734272562359</v>
+        <v>0.84708149989221204</v>
       </c>
       <c r="D71" s="0">
-        <v>0.30293559012333776</v>
+        <v>0.59625417738561726</v>
       </c>
       <c r="E71" s="0">
-        <v>0.70646499000566787</v>
+        <v>0.90277156239744549</v>
       </c>
       <c r="F71" s="0">
-        <v>0.80959138376450834</v>
+        <v>1.0788487428592211</v>
       </c>
       <c r="G71" s="0">
-        <v>0.86501709917521541</v>
+        <v>0.78455039227519552</v>
       </c>
       <c r="H71" s="0">
-        <v>0.74987218087825869</v>
+        <v>1.2043401692893248</v>
       </c>
       <c r="I71" s="0">
-        <v>0.47069571607316596</v>
+        <v>0.62362217235010176</v>
       </c>
       <c r="J71" s="0">
-        <v>0.73610599926389342</v>
+        <v>0.97534044902465866</v>
       </c>
       <c r="K71" s="0">
         <v>0</v>
       </c>
       <c r="L71" s="0">
-        <v>0.88483189749012447</v>
+        <v>0.85995085995085918</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="0">
-        <v>0.65964359554986651</v>
+        <v>0.92300876242985053</v>
       </c>
       <c r="B72" s="0">
-        <v>1.3157894736842093</v>
+        <v>0.87719298245613953</v>
       </c>
       <c r="C72" s="0">
-        <v>0.61755791983159758</v>
+        <v>0.79889422894025974</v>
       </c>
       <c r="D72" s="0">
-        <v>0.28610583511648568</v>
+        <v>0.48325439376818175</v>
       </c>
       <c r="E72" s="0">
-        <v>0.65992422208299706</v>
+        <v>0.82938035144246469</v>
       </c>
       <c r="F72" s="0">
-        <v>0.7568314958337875</v>
+        <v>1.016992322526652</v>
       </c>
       <c r="G72" s="0">
-        <v>0.6638503319251654</v>
+        <v>0.90525045262522552</v>
       </c>
       <c r="H72" s="0">
-        <v>0.86917002783616348</v>
+        <v>0.96574447537351504</v>
       </c>
       <c r="I72" s="0">
-        <v>0.49055629481043028</v>
+        <v>0.57397072550694073</v>
       </c>
       <c r="J72" s="0">
-        <v>0.40485829959514136</v>
+        <v>0.97534044902465866</v>
       </c>
       <c r="K72" s="0">
-        <v>0.12886597938144317</v>
+        <v>0</v>
       </c>
       <c r="L72" s="0">
-        <v>0.84906540602743064</v>
+        <v>0.84284514664261423</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="0">
-        <v>0.59564832135473023</v>
+        <v>0.8983951954317212</v>
       </c>
       <c r="B73" s="0">
-        <v>1.1403508771929816</v>
+        <v>0.78947368421052566</v>
       </c>
       <c r="C73" s="0">
-        <v>0.56303021849123069</v>
+        <v>0.73168566682306324</v>
       </c>
       <c r="D73" s="0">
-        <v>0.24763782367225232</v>
+        <v>0.3534248551438941</v>
       </c>
       <c r="E73" s="0">
-        <v>0.57996956949789624</v>
+        <v>0.7804528774724776</v>
       </c>
       <c r="F73" s="0">
-        <v>0.67860131717789118</v>
+        <v>0.89327948186151351</v>
       </c>
       <c r="G73" s="0">
-        <v>0.80466706900020035</v>
+        <v>0.74431703882518541</v>
       </c>
       <c r="H73" s="0">
-        <v>0.75555303073339708</v>
+        <v>0.87485087769130176</v>
       </c>
       <c r="I73" s="0">
-        <v>0.42501638497745792</v>
+        <v>0.53226351015868556</v>
       </c>
       <c r="J73" s="0">
-        <v>0.42326094957673871</v>
+        <v>0.95693779904306131</v>
       </c>
       <c r="K73" s="0">
         <v>0</v>
       </c>
       <c r="L73" s="0">
-        <v>0.75731658010138958</v>
+        <v>0.80707865517992028</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="0">
-        <v>0.55134390075809736</v>
+        <v>0.83932263463621071</v>
       </c>
       <c r="B74" s="0">
-        <v>1.1403508771929816</v>
+        <v>0.96491228070175361</v>
       </c>
       <c r="C74" s="0">
-        <v>0.50596634499549786</v>
+        <v>0.65940476039513507</v>
       </c>
       <c r="D74" s="0">
-        <v>0.2548505758180461</v>
+        <v>0.32457384656071908</v>
       </c>
       <c r="E74" s="0">
-        <v>0.51433515319669398</v>
+        <v>0.66410095766580091</v>
       </c>
       <c r="F74" s="0">
-        <v>0.67860131717789118</v>
+        <v>0.86598988465596838</v>
       </c>
       <c r="G74" s="0">
-        <v>0.54315027157513529</v>
+        <v>0.90525045262522552</v>
       </c>
       <c r="H74" s="0">
-        <v>0.63625518377549228</v>
+        <v>0.84076577856047185</v>
       </c>
       <c r="I74" s="0">
-        <v>0.41111397986137277</v>
+        <v>0.46870965819943955</v>
       </c>
       <c r="J74" s="0">
-        <v>0.44166359955833606</v>
+        <v>1.0489510489510481</v>
       </c>
       <c r="K74" s="0">
-        <v>0.12886597938144317</v>
+        <v>0</v>
       </c>
       <c r="L74" s="0">
-        <v>0.72310515348489968</v>
+        <v>0.70444437533045068</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="0">
-        <v>0.58580289455547851</v>
+        <v>0.78763414394013909</v>
       </c>
       <c r="B75" s="0">
-        <v>0.70175438596491169</v>
+        <v>1.2280701754385954</v>
       </c>
       <c r="C75" s="0">
-        <v>0.47045993482037518</v>
+        <v>0.56049404633586475</v>
       </c>
       <c r="D75" s="0">
-        <v>0.27168033082489818</v>
+        <v>0.34861635371336491</v>
       </c>
       <c r="E75" s="0">
-        <v>0.47256779736865612</v>
+        <v>0.60682001253020623</v>
       </c>
       <c r="F75" s="0">
-        <v>0.64585380053123698</v>
+        <v>0.8150493032056173</v>
       </c>
       <c r="G75" s="0">
-        <v>0.50291691812512529</v>
+        <v>0.66385033192516541</v>
       </c>
       <c r="H75" s="0">
-        <v>0.60785093449980065</v>
+        <v>0.67602113276146048</v>
       </c>
       <c r="I75" s="0">
-        <v>0.3237274334174095</v>
+        <v>0.46076542670453374</v>
       </c>
       <c r="J75" s="0">
-        <v>0.69930069930069871</v>
+        <v>0.82811924917188007</v>
       </c>
       <c r="K75" s="0">
         <v>0</v>
       </c>
       <c r="L75" s="0">
-        <v>0.64224178148228728</v>
+        <v>0.61580567909681783</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="0">
-        <v>0.53657576055921985</v>
+        <v>0.79009550063995204</v>
       </c>
       <c r="B76" s="0">
-        <v>0.26315789473684187</v>
+        <v>1.5789473684210513</v>
       </c>
       <c r="C76" s="0">
-        <v>0.4438301271890332</v>
+        <v>0.51864720577232737</v>
       </c>
       <c r="D76" s="0">
-        <v>0.28610583511648568</v>
+        <v>0.20195706008222516</v>
       </c>
       <c r="E76" s="0">
-        <v>0.4379605596825677</v>
+        <v>0.51612518273218122</v>
       </c>
       <c r="F76" s="0">
-        <v>0.60219044500236452</v>
+        <v>0.78594039951970252</v>
       </c>
       <c r="G76" s="0">
-        <v>0.52303359485013035</v>
+        <v>0.42245021122510523</v>
       </c>
       <c r="H76" s="0">
-        <v>0.4715105379764809</v>
+        <v>0.68738283247173715</v>
       </c>
       <c r="I76" s="0">
-        <v>0.34358801215467388</v>
+        <v>0.51240293142142113</v>
       </c>
       <c r="J76" s="0">
-        <v>0.58888479941111471</v>
+        <v>0.77291129922708801</v>
       </c>
       <c r="K76" s="0">
-        <v>0</v>
+        <v>0.12886597938144317</v>
       </c>
       <c r="L76" s="0">
-        <v>0.63757658694367503</v>
+        <v>0.63291139240506267</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="0">
-        <v>0.44304420596632821</v>
+        <v>0.6867185192478088</v>
       </c>
       <c r="B77" s="0">
-        <v>0.26315789473684187</v>
+        <v>1.4912280701754372</v>
       </c>
       <c r="C77" s="0">
-        <v>0.31068108903232322</v>
+        <v>0.46665567658732632</v>
       </c>
       <c r="D77" s="0">
-        <v>0.27168033082489818</v>
+        <v>0.28129733368595655</v>
       </c>
       <c r="E77" s="0">
-        <v>0.39798323339001723</v>
+        <v>0.50299829947194086</v>
       </c>
       <c r="F77" s="0">
-        <v>0.51850234690535923</v>
+        <v>0.7531928828730482</v>
       </c>
       <c r="G77" s="0">
-        <v>0.30175015087507517</v>
+        <v>0.5833836250251454</v>
       </c>
       <c r="H77" s="0">
-        <v>0.46014883826620417</v>
+        <v>0.74987218087825869</v>
       </c>
       <c r="I77" s="0">
-        <v>0.32174137554368304</v>
+        <v>0.4230303271037314</v>
       </c>
       <c r="J77" s="0">
-        <v>0.42326094957673871</v>
+        <v>0.36805299963194671</v>
       </c>
       <c r="K77" s="0">
         <v>0</v>
       </c>
       <c r="L77" s="0">
-        <v>0.60181009548098108</v>
+        <v>0.55826827978726656</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="0">
-        <v>0.46519641626464464</v>
+        <v>0.64487545535098889</v>
       </c>
       <c r="B78" s="0">
-        <v>0.35087719298245584</v>
+        <v>0.70175438596491169</v>
       </c>
       <c r="C78" s="0">
-        <v>0.33477472450829932</v>
+        <v>0.4286130942568378</v>
       </c>
       <c r="D78" s="0">
-        <v>0.21878681508907732</v>
+        <v>0.27889308297069193</v>
       </c>
       <c r="E78" s="0">
-        <v>0.32697872848235299</v>
+        <v>0.4403472657298842</v>
       </c>
       <c r="F78" s="0">
-        <v>0.53123749226794692</v>
+        <v>0.68951715606010922</v>
       </c>
       <c r="G78" s="0">
-        <v>0.30175015087507517</v>
+        <v>0.88513377590022047</v>
       </c>
       <c r="H78" s="0">
-        <v>0.3351701414531611</v>
+        <v>0.69874453218201382</v>
       </c>
       <c r="I78" s="0">
-        <v>0.27407598657424853</v>
+        <v>0.33365772278604172</v>
       </c>
       <c r="J78" s="0">
-        <v>0.34965034965034936</v>
+        <v>0.53367684946632266</v>
       </c>
       <c r="K78" s="0">
         <v>0</v>
       </c>
       <c r="L78" s="0">
-        <v>0.56604360401828702</v>
+        <v>0.52716698286318486</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="0">
-        <v>0.38151028847100488</v>
+        <v>0.5808801811558526</v>
       </c>
       <c r="B79" s="0">
-        <v>0</v>
+        <v>0.70175438596491169</v>
       </c>
       <c r="C79" s="0">
-        <v>0.2510810433812245</v>
+        <v>0.34872367136281179</v>
       </c>
       <c r="D79" s="0">
-        <v>0.16348904863799182</v>
+        <v>0.28610583511648569</v>
       </c>
       <c r="E79" s="0">
-        <v>0.27626122497687855</v>
+        <v>0.36397267221575791</v>
       </c>
       <c r="F79" s="0">
-        <v>0.48211621729796561</v>
+        <v>0.61310628388458266</v>
       </c>
       <c r="G79" s="0">
-        <v>0.34198350432508523</v>
+        <v>0.66385033192516541</v>
       </c>
       <c r="H79" s="0">
-        <v>0.42038288928023593</v>
+        <v>0.71578708174742878</v>
       </c>
       <c r="I79" s="0">
-        <v>0.20655001886754962</v>
+        <v>0.29592262318523938</v>
       </c>
       <c r="J79" s="0">
-        <v>0.44166359955833606</v>
+        <v>0.53367684946632266</v>
       </c>
       <c r="K79" s="0">
         <v>0</v>
       </c>
       <c r="L79" s="0">
-        <v>0.57848412278791972</v>
+        <v>0.53649737194040947</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="0">
-        <v>0.30274687407699097</v>
+        <v>0.52426897706015507</v>
       </c>
       <c r="B80" s="0">
-        <v>0</v>
+        <v>0.35087719298245584</v>
       </c>
       <c r="C80" s="0">
-        <v>0.21557463320610182</v>
+        <v>0.370281134683422</v>
       </c>
       <c r="D80" s="0">
-        <v>0.15627629649219807</v>
+        <v>0.24282932224172316</v>
       </c>
       <c r="E80" s="0">
-        <v>0.25716757659834699</v>
+        <v>0.33652555267161877</v>
       </c>
       <c r="F80" s="0">
-        <v>0.39842811920096027</v>
+        <v>0.58399738019866776</v>
       </c>
       <c r="G80" s="0">
-        <v>0.34198350432508523</v>
+        <v>0.64373365520016035</v>
       </c>
       <c r="H80" s="0">
-        <v>0.26699994319150122</v>
+        <v>0.71578708174742878</v>
       </c>
       <c r="I80" s="0">
-        <v>0.17278703501420015</v>
+        <v>0.32174137554368304</v>
       </c>
       <c r="J80" s="0">
-        <v>0.31284504968715471</v>
+        <v>0.58888479941111471</v>
       </c>
       <c r="K80" s="0">
         <v>0</v>
       </c>
       <c r="L80" s="0">
-        <v>0.40587192485926626</v>
+        <v>0.44163841632196021</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="0">
-        <v>0.2904400905779263</v>
+        <v>0.48734862656296107</v>
       </c>
       <c r="B81" s="0">
-        <v>0.087719298245613961</v>
+        <v>0</v>
       </c>
       <c r="C81" s="0">
-        <v>0.16485119009878377</v>
+        <v>0.24474061299280975</v>
       </c>
       <c r="D81" s="0">
-        <v>0.12021253576322928</v>
+        <v>0.22119106580434186</v>
       </c>
       <c r="E81" s="0">
-        <v>0.22077030937677117</v>
+        <v>0.28163131358334054</v>
       </c>
       <c r="F81" s="0">
-        <v>0.38205436087763311</v>
+        <v>0.50394789506240179</v>
       </c>
       <c r="G81" s="0">
-        <v>0.14081673707503506</v>
+        <v>0.60350030175015035</v>
       </c>
       <c r="H81" s="0">
-        <v>0.23291484406067128</v>
+        <v>0.53968073623814072</v>
       </c>
       <c r="I81" s="0">
-        <v>0.16881491926674727</v>
+        <v>0.24627117634207837</v>
       </c>
       <c r="J81" s="0">
-        <v>0.331247699668752</v>
+        <v>0.5152741994847253</v>
       </c>
       <c r="K81" s="0">
-        <v>0</v>
+        <v>0.12886597938144317</v>
       </c>
       <c r="L81" s="0">
-        <v>0.41364724909028672</v>
+        <v>0.46962958355363377</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="0">
-        <v>0.31259230087624618</v>
+        <v>0.47996455646352754</v>
       </c>
       <c r="B82" s="0">
-        <v>0.087719298245614932</v>
+        <v>0.17543859649122986</v>
       </c>
       <c r="C82" s="0">
-        <v>0.11539583306914991</v>
+        <v>0.20923420281768943</v>
       </c>
       <c r="D82" s="0">
-        <v>0.098574279325849112</v>
+        <v>0.22119106580434433</v>
       </c>
       <c r="E82" s="0">
-        <v>0.18675974820251393</v>
+        <v>0.26373101822847012</v>
       </c>
       <c r="F82" s="0">
-        <v>0.34748753775061303</v>
+        <v>0.51304442746425583</v>
       </c>
       <c r="G82" s="0">
-        <v>0.18105009052504711</v>
+        <v>0.32186682760008378</v>
       </c>
       <c r="H82" s="0">
-        <v>0.23291484406067386</v>
+        <v>0.51695733681759315</v>
       </c>
       <c r="I82" s="0">
-        <v>0.16285674564556976</v>
+        <v>0.23435482909972238</v>
       </c>
       <c r="J82" s="0">
-        <v>0.18402649981597538</v>
+        <v>0.40485829959514586</v>
       </c>
       <c r="K82" s="0">
         <v>0</v>
       </c>
       <c r="L82" s="0">
-        <v>0.39032127639722974</v>
+        <v>0.37788075762759693</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="0">
-        <v>0.22398345968297706</v>
+        <v>0.38643300187063073</v>
       </c>
       <c r="B83" s="0">
         <v>0.087719298245613961</v>
       </c>
       <c r="C83" s="0">
-        <v>0.10144688621463616</v>
+        <v>0.16104693186573491</v>
       </c>
       <c r="D83" s="0">
-        <v>0.076936022888466751</v>
+        <v>0.14425504291587515</v>
       </c>
       <c r="E83" s="0">
-        <v>0.14618574539813228</v>
+        <v>0.26134431218115073</v>
       </c>
       <c r="F83" s="0">
-        <v>0.28563111741803998</v>
+        <v>0.51486373394461982</v>
       </c>
       <c r="G83" s="0">
-        <v>0.18105009052504509</v>
+        <v>0.22128344397505512</v>
       </c>
       <c r="H83" s="0">
-        <v>0.20451059478497965</v>
+        <v>0.4715105379764809</v>
       </c>
       <c r="I83" s="0">
-        <v>0.1648428035192944</v>
+        <v>0.22243848185736112</v>
       </c>
       <c r="J83" s="0">
-        <v>0.165623849834376</v>
+        <v>0.44166359955833606</v>
       </c>
       <c r="K83" s="0">
         <v>0</v>
       </c>
       <c r="L83" s="0">
-        <v>0.33744907162628651</v>
+        <v>0.33589400678008247</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="0">
-        <v>0.16983361228709251</v>
+        <v>0.45535098946539293</v>
       </c>
       <c r="B84" s="0">
-        <v>0</v>
+        <v>0.087719298245613961</v>
       </c>
       <c r="C84" s="0">
-        <v>0.069744734272562364</v>
+        <v>0.13695329638975881</v>
       </c>
       <c r="D84" s="0">
-        <v>0.076936022888466751</v>
+        <v>0.088957276464789667</v>
       </c>
       <c r="E84" s="0">
-        <v>0.13842895074435382</v>
+        <v>0.19093648378531564</v>
       </c>
       <c r="F84" s="0">
-        <v>0.28563111741803998</v>
+        <v>0.451188007131681</v>
       </c>
       <c r="G84" s="0">
         <v>0.20116676725005009</v>
       </c>
       <c r="H84" s="0">
-        <v>0.17610634550928805</v>
+        <v>0.40334033971482097</v>
       </c>
       <c r="I84" s="0">
-        <v>0.12313558817103919</v>
+        <v>0.18867549800401168</v>
       </c>
       <c r="J84" s="0">
-        <v>0.073610599926389339</v>
+        <v>0.34965034965034936</v>
       </c>
       <c r="K84" s="0">
         <v>0</v>
       </c>
       <c r="L84" s="0">
-        <v>0.30012751531738846</v>
+        <v>0.29079712624016396</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="0">
-        <v>0.17475632568671837</v>
+        <v>0.3248990843753074</v>
       </c>
       <c r="B85" s="0">
-        <v>0.17543859649122792</v>
+        <v>0</v>
       </c>
       <c r="C85" s="0">
-        <v>0.078621336816343021</v>
+        <v>0.11666391914683158</v>
       </c>
       <c r="D85" s="0">
-        <v>0.088957276464789667</v>
+        <v>0.086553025749525073</v>
       </c>
       <c r="E85" s="0">
-        <v>0.11217518422387292</v>
+        <v>0.16229601121751827</v>
       </c>
       <c r="F85" s="0">
-        <v>0.18011134155659844</v>
+        <v>0.40388603864206929</v>
       </c>
       <c r="G85" s="0">
-        <v>0.14081673707503506</v>
+        <v>0.24140012070006015</v>
       </c>
       <c r="H85" s="0">
-        <v>0.19882974492984132</v>
+        <v>0.23291484406067128</v>
       </c>
       <c r="I85" s="0">
-        <v>0.095330777938869057</v>
+        <v>0.18271732438283236</v>
       </c>
       <c r="J85" s="0">
-        <v>0.11041589988958402</v>
+        <v>0.25763709974236265</v>
       </c>
       <c r="K85" s="0">
         <v>0</v>
       </c>
       <c r="L85" s="0">
-        <v>0.26125089416228631</v>
+        <v>0.25347556993126591</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="0">
-        <v>0.15260411538840196</v>
+        <v>0.31013094417642978</v>
       </c>
       <c r="B86" s="0">
-        <v>0.17543859649122792</v>
+        <v>0.087719298245613961</v>
       </c>
       <c r="C86" s="0">
-        <v>0.035506410175122662</v>
+        <v>0.097642627981587307</v>
       </c>
       <c r="D86" s="0">
-        <v>0.088957276464789667</v>
+        <v>0.064914769312143808</v>
       </c>
       <c r="E86" s="0">
-        <v>0.080551329096930024</v>
+        <v>0.14081565679167027</v>
       </c>
       <c r="F86" s="0">
-        <v>0.15646035731179259</v>
+        <v>0.37113852199541503</v>
       </c>
       <c r="G86" s="0">
-        <v>0.12070006035003007</v>
+        <v>0.24140012070006015</v>
       </c>
       <c r="H86" s="0">
-        <v>0.096574447537351504</v>
+        <v>0.26131909333636288</v>
       </c>
       <c r="I86" s="0">
-        <v>0.075470199201604665</v>
+        <v>0.15094039840320933</v>
       </c>
       <c r="J86" s="0">
-        <v>0.11041589988958402</v>
+        <v>0.23923444976076533</v>
       </c>
       <c r="K86" s="0">
         <v>0</v>
       </c>
       <c r="L86" s="0">
-        <v>0.20526855969893926</v>
+        <v>0.19593817062171473</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="0">
-        <v>0.10583833809195618</v>
+        <v>0.2338288864822288</v>
       </c>
       <c r="B87" s="0">
         <v>0.087719298245613961</v>
       </c>
       <c r="C87" s="0">
-        <v>0.032970238019756751</v>
+        <v>0.068476648194879405</v>
       </c>
       <c r="D87" s="0">
-        <v>0.084148775034260492</v>
+        <v>0.093765777895318841</v>
       </c>
       <c r="E87" s="0">
-        <v>0.065037739789373133</v>
+        <v>0.10024165398729071</v>
       </c>
       <c r="F87" s="0">
-        <v>0.14554451842957453</v>
+        <v>0.34748753775060914</v>
       </c>
       <c r="G87" s="0">
-        <v>0.060350030175015036</v>
+        <v>0.42245021122510523</v>
       </c>
       <c r="H87" s="0">
-        <v>0.16474464579901138</v>
+        <v>0.19882974492984132</v>
       </c>
       <c r="I87" s="0">
-        <v>0.067525967706698914</v>
+        <v>0.10724712518122768</v>
       </c>
       <c r="J87" s="0">
-        <v>0.092013249907986677</v>
+        <v>0.27603974972396</v>
       </c>
       <c r="K87" s="0">
-        <v>0.25773195876288635</v>
+        <v>0</v>
       </c>
       <c r="L87" s="0">
-        <v>0.19127297608310248</v>
+        <v>0.17572232762106163</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="0">
-        <v>0.10091562469233031</v>
+        <v>0.25844245348035816</v>
       </c>
       <c r="B88" s="0">
-        <v>0.26315789473684187</v>
+        <v>0.087719298245613961</v>
       </c>
       <c r="C88" s="0">
-        <v>0.026629807631341991</v>
+        <v>0.04565109879658627</v>
       </c>
       <c r="D88" s="0">
-        <v>0.040872262159497956</v>
+        <v>0.069723270742672983</v>
       </c>
       <c r="E88" s="0">
-        <v>0.048927473969987124</v>
+        <v>0.090098153286195803</v>
       </c>
       <c r="F88" s="0">
-        <v>0.10551977586144153</v>
+        <v>0.23105192300694952</v>
       </c>
       <c r="G88" s="0">
-        <v>0.060350030175015036</v>
+        <v>0.20116676725005009</v>
       </c>
       <c r="H88" s="0">
-        <v>0.090893597682213167</v>
+        <v>0.27836164290177784</v>
       </c>
       <c r="I88" s="0">
-        <v>0.041707215348255215</v>
+        <v>0.085400488570236868</v>
       </c>
       <c r="J88" s="0">
-        <v>0.11041589988958402</v>
+        <v>0.23923444976076533</v>
       </c>
       <c r="K88" s="0">
-        <v>0.25773195876288635</v>
+        <v>0</v>
       </c>
       <c r="L88" s="0">
-        <v>0.17416726277485756</v>
+        <v>0.14306596585077586</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="0">
-        <v>0.088608841193265647</v>
+        <v>0.19198582258540892</v>
       </c>
       <c r="B89" s="0">
         <v>0.087719298245613961</v>
       </c>
       <c r="C89" s="0">
-        <v>0.013948946854512471</v>
+        <v>0.025361721553659039</v>
       </c>
       <c r="D89" s="0">
-        <v>0.045680763590027124</v>
+        <v>0.081744524318995912</v>
       </c>
       <c r="E89" s="0">
-        <v>0.042364032339866901</v>
+        <v>0.072197857931322468</v>
       </c>
       <c r="F89" s="0">
-        <v>0.083688098097005351</v>
+        <v>0.24924498781064636</v>
       </c>
       <c r="G89" s="0">
-        <v>0.020116676725005011</v>
+        <v>0.22128344397505512</v>
       </c>
       <c r="H89" s="0">
-        <v>0.06248934840652156</v>
+        <v>0.19314889507470301</v>
       </c>
       <c r="I89" s="0">
-        <v>0.029790868105896578</v>
+        <v>0.065539909832972476</v>
       </c>
       <c r="J89" s="0">
-        <v>0.073610599926389339</v>
+        <v>0.14722119985277868</v>
       </c>
       <c r="K89" s="0">
-        <v>0.64432989690721587</v>
+        <v>0.25773195876288635</v>
       </c>
       <c r="L89" s="0">
-        <v>0.11973999315771458</v>
+        <v>0.10107921500326555</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="0">
-        <v>0.044304420596632824</v>
+        <v>0.2190607462833512</v>
       </c>
       <c r="B90" s="0">
-        <v>0.26315789473684187</v>
+        <v>0.17543859649122792</v>
       </c>
       <c r="C90" s="0">
-        <v>0.0076085164660977117</v>
+        <v>0.029165979786707895</v>
       </c>
       <c r="D90" s="0">
-        <v>0.026446757867910439</v>
+        <v>0.081744524318995912</v>
       </c>
       <c r="E90" s="0">
-        <v>0.033413884662430234</v>
+        <v>0.053104209552790903</v>
       </c>
       <c r="F90" s="0">
-        <v>0.060037113852199495</v>
+        <v>0.20558163228177401</v>
       </c>
       <c r="G90" s="0">
-        <v>0.060350030175015036</v>
+        <v>0.16093341380004009</v>
       </c>
       <c r="H90" s="0">
-        <v>0.068170198261659889</v>
+        <v>0.19882974492984132</v>
       </c>
       <c r="I90" s="0">
-        <v>0.017874520863537947</v>
+        <v>0.057595678338066718</v>
       </c>
       <c r="J90" s="0">
-        <v>0.055207949944792008</v>
+        <v>0.18402649981597335</v>
       </c>
       <c r="K90" s="0">
-        <v>0.38659793814432958</v>
+        <v>0.5154639175257727</v>
       </c>
       <c r="L90" s="0">
-        <v>0.11351973377289823</v>
+        <v>0.08552856654122469</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="0">
-        <v>0.024613566998129346</v>
+        <v>0.1279905483902726</v>
       </c>
       <c r="B91" s="0">
-        <v>0.26315789473684187</v>
+        <v>0.35087719298245584</v>
       </c>
       <c r="C91" s="0">
-        <v>0.0025361721553659039</v>
+        <v>0.016485119009878375</v>
       </c>
       <c r="D91" s="0">
-        <v>0.012021253576322928</v>
+        <v>0.050489265020556291</v>
       </c>
       <c r="E91" s="0">
-        <v>0.019690324890360673</v>
+        <v>0.035203914197917567</v>
       </c>
       <c r="F91" s="0">
-        <v>0.043663355528872357</v>
+        <v>0.14918313139031389</v>
       </c>
       <c r="G91" s="0">
-        <v>0.020116676725005011</v>
+        <v>0.18105009052504509</v>
       </c>
       <c r="H91" s="0">
-        <v>0.022723399420553292</v>
+        <v>0.13065954666818144</v>
       </c>
       <c r="I91" s="0">
-        <v>0.01390240511608507</v>
+        <v>0.03972115747452877</v>
       </c>
       <c r="J91" s="0">
         <v>0.073610599926389339</v>
       </c>
       <c r="K91" s="0">
-        <v>1.1597938144329887</v>
+        <v>0.5154639175257727</v>
       </c>
       <c r="L91" s="0">
-        <v>0.087083631387428778</v>
+        <v>0.076198177464000191</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="0">
-        <v>0.017229496898690543</v>
+        <v>0.10829969479176912</v>
       </c>
       <c r="B92" s="0">
-        <v>0.17543859649122792</v>
+        <v>0.087719298245613961</v>
       </c>
       <c r="C92" s="0">
-        <v>0.0063404303884147598</v>
+        <v>0.0076085164660977117</v>
       </c>
       <c r="D92" s="0">
-        <v>0.016829755006852101</v>
+        <v>0.050489265020556291</v>
       </c>
       <c r="E92" s="0">
-        <v>0.0089501476774366696</v>
+        <v>0.038187296757063123</v>
       </c>
       <c r="F92" s="0">
-        <v>0.034566823127023943</v>
+        <v>0.10370046938107184</v>
       </c>
       <c r="G92" s="0">
-        <v>0.020116676725005011</v>
+        <v>0.040233353450010022</v>
       </c>
       <c r="H92" s="0">
-        <v>0.034085099130829945</v>
+        <v>0.15906379594387307</v>
       </c>
       <c r="I92" s="0">
-        <v>0.0079442314949057548</v>
+        <v>0.021846636610990827</v>
       </c>
       <c r="J92" s="0">
-        <v>0.03680529996319467</v>
+        <v>0.11041589988958402</v>
       </c>
       <c r="K92" s="0">
-        <v>1.0309278350515454</v>
+        <v>0.5154639175257727</v>
       </c>
       <c r="L92" s="0">
-        <v>0.048207010232326646</v>
+        <v>0.037321556308898045</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="0">
-        <v>0.012306783499064673</v>
+        <v>0.10091562469233031</v>
       </c>
       <c r="B93" s="0">
-        <v>0.43859649122806976</v>
+        <v>0.17543859649122792</v>
       </c>
       <c r="C93" s="0">
-        <v>0.0025361721553659039</v>
+        <v>0.0050723443107318078</v>
       </c>
       <c r="D93" s="0">
-        <v>0.002404250715264586</v>
+        <v>0.033659510013704201</v>
       </c>
       <c r="E93" s="0">
-        <v>0.0065634416301202248</v>
+        <v>0.017303618843044228</v>
       </c>
       <c r="F93" s="0">
-        <v>0.018193064803696816</v>
+        <v>0.098242549939962814</v>
       </c>
       <c r="G93" s="0">
-        <v>0.020116676725005011</v>
+        <v>0.12070006035003007</v>
       </c>
       <c r="H93" s="0">
-        <v>0.034085099130829945</v>
+        <v>0.073851048116798199</v>
       </c>
       <c r="I93" s="0">
-        <v>0</v>
+        <v>0.017874520863537947</v>
       </c>
       <c r="J93" s="0">
-        <v>0.018402649981597335</v>
+        <v>0.03680529996319467</v>
       </c>
       <c r="K93" s="0">
-        <v>1.5463917525773183</v>
+        <v>0.77319587628865916</v>
       </c>
       <c r="L93" s="0">
-        <v>0.043541815693714389</v>
+        <v>0.034211426616489876</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="0">
-        <v>0.0073840700994388855</v>
+        <v>0.068917987594762933</v>
       </c>
       <c r="B94" s="0">
-        <v>0.087719298245614932</v>
+        <v>0.17543859649122986</v>
       </c>
       <c r="C94" s="0">
-        <v>0</v>
+        <v>0.0038042582330488979</v>
       </c>
       <c r="D94" s="0">
-        <v>0.0096170028610584497</v>
+        <v>0.014425504291587673</v>
       </c>
       <c r="E94" s="0">
-        <v>0.0047734120946329433</v>
+        <v>0.014320236283898832</v>
       </c>
       <c r="F94" s="0">
-        <v>0</v>
+        <v>0.061856420332569856</v>
       </c>
       <c r="G94" s="0">
-        <v>0</v>
+        <v>0.080466706900020946</v>
       </c>
       <c r="H94" s="0">
-        <v>0.0056808498551383863</v>
+        <v>0.090893597682214181</v>
       </c>
       <c r="I94" s="0">
-        <v>0</v>
+        <v>0.015888462989811687</v>
       </c>
       <c r="J94" s="0">
-        <v>0.036805299963195072</v>
+        <v>0.055207949944792618</v>
       </c>
       <c r="K94" s="0">
-        <v>1.4175257731958908</v>
+        <v>1.5463917525773354</v>
       </c>
       <c r="L94" s="0">
-        <v>0.017105713308245129</v>
+        <v>0.034211426616490258</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="0">
-        <v>0.0049227133996258693</v>
+        <v>0.061533917495323366</v>
       </c>
       <c r="B95" s="0">
-        <v>0</v>
+        <v>0.087719298245613961</v>
       </c>
       <c r="C95" s="0">
-        <v>0.001268086077682952</v>
+        <v>0.0038042582330488559</v>
       </c>
       <c r="D95" s="0">
-        <v>0</v>
+        <v>0.0072127521457937566</v>
       </c>
       <c r="E95" s="0">
-        <v>0.0029833825591455568</v>
+        <v>0.007160118141949336</v>
       </c>
       <c r="F95" s="0">
-        <v>0.0018193064803696812</v>
+        <v>0.0291089036859149</v>
       </c>
       <c r="G95" s="0">
-        <v>0</v>
+        <v>0.080466706900020044</v>
       </c>
       <c r="H95" s="0">
-        <v>0</v>
+        <v>0.073851048116798199</v>
       </c>
       <c r="I95" s="0">
-        <v>0.0019860578737264387</v>
+        <v>0.0039721157474528774</v>
       </c>
       <c r="J95" s="0">
-        <v>0.018402649981597335</v>
+        <v>0.073610599926389339</v>
       </c>
       <c r="K95" s="0">
         <v>1.0309278350515454</v>
       </c>
       <c r="L95" s="0">
-        <v>0.021770907846857195</v>
+        <v>0.007775324231020426</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="0">
-        <v>0.0073840700994388039</v>
+        <v>0.049227133996258693</v>
       </c>
       <c r="B96" s="0">
-        <v>0</v>
+        <v>0.43859649122806976</v>
       </c>
       <c r="C96" s="0">
-        <v>0</v>
+        <v>0.0025361721553659039</v>
       </c>
       <c r="D96" s="0">
-        <v>0</v>
+        <v>0.012021253576322928</v>
       </c>
       <c r="E96" s="0">
-        <v>0.0011933530236582226</v>
+        <v>0.0023867060473164452</v>
       </c>
       <c r="F96" s="0">
-        <v>0</v>
+        <v>0.0291089036859149</v>
       </c>
       <c r="G96" s="0">
-        <v>0</v>
+        <v>0.020116676725005011</v>
       </c>
       <c r="H96" s="0">
-        <v>0</v>
+        <v>0.051127648696244914</v>
       </c>
       <c r="I96" s="0">
-        <v>0</v>
+        <v>0.0019860578737264387</v>
       </c>
       <c r="J96" s="0">
-        <v>0</v>
+        <v>0.018402649981597335</v>
       </c>
       <c r="K96" s="0">
-        <v>0.90206185567010222</v>
+        <v>1.0309278350515454</v>
       </c>
       <c r="L96" s="0">
-        <v>0.007775324231020426</v>
+        <v>0.0062202593848163417</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="0">
-        <v>0.0024613566998129346</v>
+        <v>0.027074923697942281</v>
       </c>
       <c r="B97" s="0">
-        <v>0</v>
+        <v>0.17543859649122792</v>
       </c>
       <c r="C97" s="0">
-        <v>0</v>
+        <v>0.001268086077682952</v>
       </c>
       <c r="D97" s="0">
-        <v>0</v>
+        <v>0.002404250715264586</v>
       </c>
       <c r="E97" s="0">
-        <v>0.0005966765118291113</v>
+        <v>0.0023867060473164452</v>
       </c>
       <c r="F97" s="0">
-        <v>0.0036386129607393625</v>
+        <v>0.016373758323327131</v>
       </c>
       <c r="G97" s="0">
-        <v>0.020116676725005011</v>
+        <v>0</v>
       </c>
       <c r="H97" s="0">
-        <v>0</v>
+        <v>0.028404249275691615</v>
       </c>
       <c r="I97" s="0">
-        <v>0</v>
+        <v>0.0039721157474528774</v>
       </c>
       <c r="J97" s="0">
-        <v>0</v>
+        <v>0.03680529996319467</v>
       </c>
       <c r="K97" s="0">
-        <v>1.0309278350515454</v>
+        <v>0.77319587628865916</v>
       </c>
       <c r="L97" s="0">
-        <v>0.0031101296924081708</v>
+        <v>0.0046651945386122556</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="0">
-        <v>0</v>
+        <v>0.027074923697942281</v>
       </c>
       <c r="B98" s="0">
-        <v>0</v>
+        <v>0.17543859649122792</v>
       </c>
       <c r="C98" s="0">
         <v>0</v>
       </c>
       <c r="D98" s="0">
-        <v>0</v>
+        <v>0.002404250715264586</v>
       </c>
       <c r="E98" s="0">
-        <v>0</v>
+        <v>0.0005966765118291113</v>
       </c>
       <c r="F98" s="0">
-        <v>0</v>
+        <v>0.0072772259214787249</v>
       </c>
       <c r="G98" s="0">
-        <v>0</v>
+        <v>0.020116676725005011</v>
       </c>
       <c r="H98" s="0">
-        <v>0</v>
+        <v>0.022723399420553292</v>
       </c>
       <c r="I98" s="0">
-        <v>0</v>
+        <v>0.0019860578737264387</v>
       </c>
       <c r="J98" s="0">
-        <v>0</v>
+        <v>0.018402649981597335</v>
       </c>
       <c r="K98" s="0">
-        <v>0.12886597938144317</v>
+        <v>1.1597938144329887</v>
       </c>
       <c r="L98" s="0">
-        <v>0.0062202593848163417</v>
+        <v>0.0046651945386122556</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="0">
-        <v>0</v>
+        <v>0.012306783499064673</v>
       </c>
       <c r="B99" s="0">
         <v>0</v>
       </c>
       <c r="C99" s="0">
-        <v>0</v>
+        <v>0.001268086077682952</v>
       </c>
       <c r="D99" s="0">
         <v>0</v>
       </c>
       <c r="E99" s="0">
-        <v>0</v>
+        <v>0.0005966765118291113</v>
       </c>
       <c r="F99" s="0">
-        <v>0</v>
+        <v>0.0090965324018484079</v>
       </c>
       <c r="G99" s="0">
-        <v>0</v>
+        <v>0.040233353450010022</v>
       </c>
       <c r="H99" s="0">
-        <v>0</v>
+        <v>0.028404249275691615</v>
       </c>
       <c r="I99" s="0">
-        <v>0</v>
+        <v>0.0039721157474528774</v>
       </c>
       <c r="J99" s="0">
         <v>0</v>
       </c>
       <c r="K99" s="0">
-        <v>0.12886597938144317</v>
+        <v>0.90206185567010222</v>
       </c>
       <c r="L99" s="0">
         <v>0.0015550648462040854</v>
@@ -3834,7 +3835,7 @@
     </row>
     <row r="100">
       <c r="A100" s="0">
-        <v>0</v>
+        <v>0.0098454267992517386</v>
       </c>
       <c r="B100" s="0">
         <v>0</v>
@@ -3849,22 +3850,22 @@
         <v>0</v>
       </c>
       <c r="F100" s="0">
-        <v>0</v>
+        <v>0.0072772259214787249</v>
       </c>
       <c r="G100" s="0">
         <v>0</v>
       </c>
       <c r="H100" s="0">
-        <v>0</v>
+        <v>0.011361699710276646</v>
       </c>
       <c r="I100" s="0">
-        <v>0</v>
+        <v>0.0019860578737264387</v>
       </c>
       <c r="J100" s="0">
         <v>0</v>
       </c>
       <c r="K100" s="0">
-        <v>0</v>
+        <v>0.90206185567010222</v>
       </c>
       <c r="L100" s="0">
         <v>0</v>

--- a/braph2individualconnectome/pipelines/neuroimaging conversion structural/Example data NIfTI/reference_data/pdf_wmprob/sub-0007_ses-01_WMprob_pdf.xlsx
+++ b/braph2individualconnectome/pipelines/neuroimaging conversion structural/Example data NIfTI/reference_data/pdf_wmprob/sub-0007_ses-01_WMprob_pdf.xlsx
@@ -1,7 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <fileVersion appName="libxl" rupBuild="4.6.0"/>
   <workbookPr/>
   <bookViews>
     <workbookView activeTab="0"/>
